--- a/results/dataset1_ANN_CPU_model_results.xlsx
+++ b/results/dataset1_ANN_CPU_model_results.xlsx
@@ -7,14 +7,19 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Rank_1_Best" sheetId="1" r:id="rId1"/>
+    <sheet name="Rank_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Rank_3" sheetId="3" r:id="rId3"/>
+    <sheet name="Rank_4" sheetId="4" r:id="rId4"/>
+    <sheet name="Rank_5" sheetId="5" r:id="rId5"/>
+    <sheet name="All_Combinations" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="31">
   <si>
     <t>Observation</t>
   </si>
@@ -46,10 +51,10 @@
     <t>alpha</t>
   </si>
   <si>
-    <t>avg_rmse</t>
+    <t>rmse</t>
   </si>
   <si>
-    <t>avg_mae</t>
+    <t>mae</t>
   </si>
   <si>
     <t>r2</t>
@@ -62,6 +67,51 @@
   </si>
   <si>
     <t>0.95</t>
+  </si>
+  <si>
+    <t>(5, 5)</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>(3, 2)</t>
+  </si>
+  <si>
+    <t>(5, 3)</t>
+  </si>
+  <si>
+    <t>(6, 4)</t>
+  </si>
+  <si>
+    <t>(8, 4)</t>
+  </si>
+  <si>
+    <t>(8, 8)</t>
+  </si>
+  <si>
+    <t>(4, 1)</t>
+  </si>
+  <si>
+    <t>(1, 4)</t>
+  </si>
+  <si>
+    <t>tanh</t>
   </si>
 </sst>
 </file>
@@ -440,13 +490,13 @@
         <v>11.558</v>
       </c>
       <c r="C2">
-        <v>14.23827855443216</v>
+        <v>14.238</v>
       </c>
       <c r="D2">
-        <v>2.680278554432157</v>
+        <v>2.68</v>
       </c>
       <c r="E2">
-        <v>7.183893129348931</v>
+        <v>7.182399999999999</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
@@ -463,13 +513,13 @@
         <v>14.717</v>
       </c>
       <c r="C3">
-        <v>13.68159234690653</v>
+        <v>13.682</v>
       </c>
       <c r="D3">
-        <v>1.035407653093472</v>
+        <v>1.035</v>
       </c>
       <c r="E3">
-        <v>1.072069008084531</v>
+        <v>1.071225</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -486,13 +536,13 @@
         <v>14.867</v>
       </c>
       <c r="C4">
-        <v>13.66742413375566</v>
+        <v>13.667</v>
       </c>
       <c r="D4">
-        <v>1.199575866244345</v>
+        <v>1.200000000000001</v>
       </c>
       <c r="E4">
-        <v>1.438982258875871</v>
+        <v>1.440000000000003</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -509,13 +559,13 @@
         <v>7.647</v>
       </c>
       <c r="C5">
-        <v>9.417621557278231</v>
+        <v>9.417999999999999</v>
       </c>
       <c r="D5">
-        <v>1.770621557278231</v>
+        <v>1.770999999999999</v>
       </c>
       <c r="E5">
-        <v>3.135100699098388</v>
+        <v>3.136440999999996</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -532,13 +582,13 @@
         <v>6.245</v>
       </c>
       <c r="C6">
-        <v>7.859245222065052</v>
+        <v>7.859</v>
       </c>
       <c r="D6">
-        <v>1.614245222065052</v>
+        <v>1.614</v>
       </c>
       <c r="E6">
-        <v>2.605787636959849</v>
+        <v>2.604995999999999</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -555,13 +605,13 @@
         <v>14.514</v>
       </c>
       <c r="C7">
-        <v>14.4744206821121</v>
+        <v>14.474</v>
       </c>
       <c r="D7">
-        <v>0.0395793178879007</v>
+        <v>0.03999999999999915</v>
       </c>
       <c r="E7">
-        <v>0.001566522404471496</v>
+        <v>0.001599999999999932</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
@@ -578,13 +628,13 @@
         <v>13.608</v>
       </c>
       <c r="C8">
-        <v>14.98822608617601</v>
+        <v>14.988</v>
       </c>
       <c r="D8">
-        <v>1.380226086176005</v>
+        <v>1.379999999999999</v>
       </c>
       <c r="E8">
-        <v>1.905024048960734</v>
+        <v>1.904399999999997</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -595,13 +645,13 @@
         <v>10.168</v>
       </c>
       <c r="C9">
-        <v>9.817835064468511</v>
+        <v>9.818</v>
       </c>
       <c r="D9">
-        <v>0.3501649355314882</v>
+        <v>0.3499999999999996</v>
       </c>
       <c r="E9">
-        <v>0.1226154820757713</v>
+        <v>0.1224999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -612,13 +662,13 @@
         <v>10.325</v>
       </c>
       <c r="C10">
-        <v>14.10564083943656</v>
+        <v>14.106</v>
       </c>
       <c r="D10">
-        <v>3.780640839436561</v>
+        <v>3.781000000000001</v>
       </c>
       <c r="E10">
-        <v>14.29324515681559</v>
+        <v>14.295961</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -629,13 +679,13 @@
         <v>15.851</v>
       </c>
       <c r="C11">
-        <v>13.57468501171723</v>
+        <v>13.575</v>
       </c>
       <c r="D11">
-        <v>2.276314988282767</v>
+        <v>2.276000000000002</v>
       </c>
       <c r="E11">
-        <v>5.181609925880773</v>
+        <v>5.180176000000007</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -646,13 +696,13 @@
         <v>9.039999999999999</v>
       </c>
       <c r="C12">
-        <v>9.282307177362839</v>
+        <v>9.282</v>
       </c>
       <c r="D12">
-        <v>0.2423071773628394</v>
+        <v>0.2420000000000009</v>
       </c>
       <c r="E12">
-        <v>0.05871276820154649</v>
+        <v>0.05856400000000043</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -663,13 +713,13 @@
         <v>14.514</v>
       </c>
       <c r="C13">
-        <v>14.95862948112464</v>
+        <v>14.959</v>
       </c>
       <c r="D13">
-        <v>0.444629481124645</v>
+        <v>0.4450000000000003</v>
       </c>
       <c r="E13">
-        <v>0.197695375485171</v>
+        <v>0.1980250000000003</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -680,13 +730,13 @@
         <v>16.24</v>
       </c>
       <c r="C14">
-        <v>13.53728192761283</v>
+        <v>13.537</v>
       </c>
       <c r="D14">
-        <v>2.702718072387169</v>
+        <v>2.702999999999998</v>
       </c>
       <c r="E14">
-        <v>7.304684978808215</v>
+        <v>7.306208999999988</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -697,13 +747,13 @@
         <v>11.728</v>
       </c>
       <c r="C15">
-        <v>14.30861938968455</v>
+        <v>14.309</v>
       </c>
       <c r="D15">
-        <v>2.580619389684548</v>
+        <v>2.581</v>
       </c>
       <c r="E15">
-        <v>6.65959643441585</v>
+        <v>6.661560999999997</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -714,13 +764,13 @@
         <v>12.485</v>
       </c>
       <c r="C16">
-        <v>13.89346248645516</v>
+        <v>13.893</v>
       </c>
       <c r="D16">
-        <v>1.408462486455157</v>
+        <v>1.408000000000001</v>
       </c>
       <c r="E16">
-        <v>1.983766575751444</v>
+        <v>1.982464000000004</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -731,13 +781,13 @@
         <v>10.008</v>
       </c>
       <c r="C17">
-        <v>9.399558446892186</v>
+        <v>9.4</v>
       </c>
       <c r="D17">
-        <v>0.6084415531078129</v>
+        <v>0.6079999999999988</v>
       </c>
       <c r="E17">
-        <v>0.3702011235482475</v>
+        <v>0.3696639999999985</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -748,13 +798,13 @@
         <v>12.512</v>
       </c>
       <c r="C18">
-        <v>13.18447182661791</v>
+        <v>13.184</v>
       </c>
       <c r="D18">
-        <v>0.6724718266179099</v>
+        <v>0.6719999999999988</v>
       </c>
       <c r="E18">
-        <v>0.4522183575948283</v>
+        <v>0.4515839999999984</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -765,13 +815,13 @@
         <v>6.301</v>
       </c>
       <c r="C19">
-        <v>6.893709812085038</v>
+        <v>6.894</v>
       </c>
       <c r="D19">
-        <v>0.5927098120850376</v>
+        <v>0.593</v>
       </c>
       <c r="E19">
-        <v>0.3513049213418806</v>
+        <v>0.351649</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -782,13 +832,13 @@
         <v>9.577</v>
       </c>
       <c r="C20">
-        <v>10.75663179829822</v>
+        <v>10.757</v>
       </c>
       <c r="D20">
-        <v>1.179631798298225</v>
+        <v>1.18</v>
       </c>
       <c r="E20">
-        <v>1.391531179556303</v>
+        <v>1.392399999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -799,13 +849,13 @@
         <v>12.629</v>
       </c>
       <c r="C21">
-        <v>10.89737184078479</v>
+        <v>10.897</v>
       </c>
       <c r="D21">
-        <v>1.731628159215214</v>
+        <v>1.731999999999999</v>
       </c>
       <c r="E21">
-        <v>2.998536081787071</v>
+        <v>2.999823999999998</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -816,13 +866,13 @@
         <v>10.389</v>
       </c>
       <c r="C22">
-        <v>11.97456595414176</v>
+        <v>11.975</v>
       </c>
       <c r="D22">
-        <v>1.585565954141757</v>
+        <v>1.586</v>
       </c>
       <c r="E22">
-        <v>2.514019394933459</v>
+        <v>2.515396000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -833,13 +883,13 @@
         <v>12.196</v>
       </c>
       <c r="C23">
-        <v>13.38027951341489</v>
+        <v>13.38</v>
       </c>
       <c r="D23">
-        <v>1.184279513414888</v>
+        <v>1.184000000000001</v>
       </c>
       <c r="E23">
-        <v>1.402517965894203</v>
+        <v>1.401856000000002</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -850,13 +900,13 @@
         <v>7.545</v>
       </c>
       <c r="C24">
-        <v>8.123164203479663</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="D24">
-        <v>0.5781642034796626</v>
+        <v>0.5779999999999994</v>
       </c>
       <c r="E24">
-        <v>0.3342738461852727</v>
+        <v>0.3340839999999993</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -867,13 +917,13 @@
         <v>6.753</v>
       </c>
       <c r="C25">
-        <v>8.375082667902873</v>
+        <v>8.375</v>
       </c>
       <c r="D25">
-        <v>1.622082667902873</v>
+        <v>1.622</v>
       </c>
       <c r="E25">
-        <v>2.631152181510903</v>
+        <v>2.630884</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -884,13 +934,13 @@
         <v>13.289</v>
       </c>
       <c r="C26">
-        <v>11.95466540777995</v>
+        <v>11.955</v>
       </c>
       <c r="D26">
-        <v>1.334334592220054</v>
+        <v>1.334</v>
       </c>
       <c r="E26">
-        <v>1.780448803995059</v>
+        <v>1.779555999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -901,13 +951,13 @@
         <v>9.148999999999999</v>
       </c>
       <c r="C27">
-        <v>10.75278048237293</v>
+        <v>10.753</v>
       </c>
       <c r="D27">
-        <v>1.603780482372935</v>
+        <v>1.604000000000001</v>
       </c>
       <c r="E27">
-        <v>2.572111835640364</v>
+        <v>2.572816000000003</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -918,13 +968,13 @@
         <v>18.214</v>
       </c>
       <c r="C28">
-        <v>14.05906994634739</v>
+        <v>14.059</v>
       </c>
       <c r="D28">
-        <v>4.154930053652611</v>
+        <v>4.154999999999999</v>
       </c>
       <c r="E28">
-        <v>17.26344375074569</v>
+        <v>17.26402499999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -935,13 +985,13 @@
         <v>16.758</v>
       </c>
       <c r="C29">
-        <v>14.52916994565534</v>
+        <v>14.529</v>
       </c>
       <c r="D29">
-        <v>2.228830054344662</v>
+        <v>2.228999999999999</v>
       </c>
       <c r="E29">
-        <v>4.967683411150031</v>
+        <v>4.968440999999997</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -952,13 +1002,13 @@
         <v>14.814</v>
       </c>
       <c r="C30">
-        <v>14.84881042160616</v>
+        <v>14.849</v>
       </c>
       <c r="D30">
-        <v>0.03481042160615644</v>
+        <v>0.03500000000000014</v>
       </c>
       <c r="E30">
-        <v>0.001211765452398363</v>
+        <v>0.00122500000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -969,13 +1019,7418 @@
         <v>14.322</v>
       </c>
       <c r="C31">
-        <v>12.57714202189773</v>
+        <v>12.577</v>
       </c>
       <c r="D31">
-        <v>1.744857978102267</v>
+        <v>1.744999999999999</v>
       </c>
       <c r="E31">
-        <v>3.044529363747132</v>
+        <v>3.045024999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>11.558</v>
+      </c>
+      <c r="C2">
+        <v>14.249</v>
+      </c>
+      <c r="D2">
+        <v>2.691000000000001</v>
+      </c>
+      <c r="E2">
+        <v>7.241481000000004</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>14.717</v>
+      </c>
+      <c r="C3">
+        <v>13.676</v>
+      </c>
+      <c r="D3">
+        <v>1.041</v>
+      </c>
+      <c r="E3">
+        <v>1.083681000000001</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>14.867</v>
+      </c>
+      <c r="C4">
+        <v>13.662</v>
+      </c>
+      <c r="D4">
+        <v>1.205</v>
+      </c>
+      <c r="E4">
+        <v>1.452025</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7.647</v>
+      </c>
+      <c r="C5">
+        <v>8.276</v>
+      </c>
+      <c r="D5">
+        <v>0.6289999999999996</v>
+      </c>
+      <c r="E5">
+        <v>0.3956409999999995</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>1.79017194096169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6.245</v>
+      </c>
+      <c r="C6">
+        <v>7.692</v>
+      </c>
+      <c r="D6">
+        <v>1.447</v>
+      </c>
+      <c r="E6">
+        <v>2.093809</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>1.464022474616932</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14.514</v>
+      </c>
+      <c r="C7">
+        <v>14.548</v>
+      </c>
+      <c r="D7">
+        <v>0.0340000000000007</v>
+      </c>
+      <c r="E7">
+        <v>0.001156000000000047</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.6881899947750428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>13.608</v>
+      </c>
+      <c r="C8">
+        <v>15.133</v>
+      </c>
+      <c r="D8">
+        <v>1.524999999999999</v>
+      </c>
+      <c r="E8">
+        <v>2.325624999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.168</v>
+      </c>
+      <c r="C9">
+        <v>9.507</v>
+      </c>
+      <c r="D9">
+        <v>0.6609999999999996</v>
+      </c>
+      <c r="E9">
+        <v>0.4369209999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>10.325</v>
+      </c>
+      <c r="C10">
+        <v>14.101</v>
+      </c>
+      <c r="D10">
+        <v>3.776000000000002</v>
+      </c>
+      <c r="E10">
+        <v>14.25817600000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>15.851</v>
+      </c>
+      <c r="C11">
+        <v>13.566</v>
+      </c>
+      <c r="D11">
+        <v>2.285</v>
+      </c>
+      <c r="E11">
+        <v>5.221225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C12">
+        <v>9.369</v>
+      </c>
+      <c r="D12">
+        <v>0.3290000000000006</v>
+      </c>
+      <c r="E12">
+        <v>0.1082410000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>14.514</v>
+      </c>
+      <c r="C13">
+        <v>15.105</v>
+      </c>
+      <c r="D13">
+        <v>0.5910000000000011</v>
+      </c>
+      <c r="E13">
+        <v>0.3492810000000013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>16.24</v>
+      </c>
+      <c r="C14">
+        <v>13.528</v>
+      </c>
+      <c r="D14">
+        <v>2.711999999999998</v>
+      </c>
+      <c r="E14">
+        <v>7.354943999999989</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.728</v>
+      </c>
+      <c r="C15">
+        <v>14.355</v>
+      </c>
+      <c r="D15">
+        <v>2.627000000000001</v>
+      </c>
+      <c r="E15">
+        <v>6.901129000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>12.485</v>
+      </c>
+      <c r="C16">
+        <v>13.889</v>
+      </c>
+      <c r="D16">
+        <v>1.404</v>
+      </c>
+      <c r="E16">
+        <v>1.971216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>10.008</v>
+      </c>
+      <c r="C17">
+        <v>9.494999999999999</v>
+      </c>
+      <c r="D17">
+        <v>0.5129999999999999</v>
+      </c>
+      <c r="E17">
+        <v>0.2631689999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>12.512</v>
+      </c>
+      <c r="C18">
+        <v>12.999</v>
+      </c>
+      <c r="D18">
+        <v>0.4870000000000001</v>
+      </c>
+      <c r="E18">
+        <v>0.2371690000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>6.301</v>
+      </c>
+      <c r="C19">
+        <v>6.509</v>
+      </c>
+      <c r="D19">
+        <v>0.2080000000000002</v>
+      </c>
+      <c r="E19">
+        <v>0.04326400000000008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.577</v>
+      </c>
+      <c r="C20">
+        <v>11.182</v>
+      </c>
+      <c r="D20">
+        <v>1.605</v>
+      </c>
+      <c r="E20">
+        <v>2.576025000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>12.629</v>
+      </c>
+      <c r="C21">
+        <v>10.992</v>
+      </c>
+      <c r="D21">
+        <v>1.636999999999999</v>
+      </c>
+      <c r="E21">
+        <v>2.679768999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>10.389</v>
+      </c>
+      <c r="C22">
+        <v>11.543</v>
+      </c>
+      <c r="D22">
+        <v>1.154</v>
+      </c>
+      <c r="E22">
+        <v>1.331716</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>12.196</v>
+      </c>
+      <c r="C23">
+        <v>13.363</v>
+      </c>
+      <c r="D23">
+        <v>1.167</v>
+      </c>
+      <c r="E23">
+        <v>1.361888999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7.545</v>
+      </c>
+      <c r="C24">
+        <v>8.199</v>
+      </c>
+      <c r="D24">
+        <v>0.6539999999999999</v>
+      </c>
+      <c r="E24">
+        <v>0.4277159999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6.753</v>
+      </c>
+      <c r="C25">
+        <v>8.378</v>
+      </c>
+      <c r="D25">
+        <v>1.625</v>
+      </c>
+      <c r="E25">
+        <v>2.640625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>13.289</v>
+      </c>
+      <c r="C26">
+        <v>11.64</v>
+      </c>
+      <c r="D26">
+        <v>1.648999999999999</v>
+      </c>
+      <c r="E26">
+        <v>2.719200999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>9.148999999999999</v>
+      </c>
+      <c r="C27">
+        <v>10.649</v>
+      </c>
+      <c r="D27">
+        <v>1.5</v>
+      </c>
+      <c r="E27">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>18.214</v>
+      </c>
+      <c r="C28">
+        <v>13.796</v>
+      </c>
+      <c r="D28">
+        <v>4.417999999999999</v>
+      </c>
+      <c r="E28">
+        <v>19.51872399999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>16.758</v>
+      </c>
+      <c r="C29">
+        <v>14.48</v>
+      </c>
+      <c r="D29">
+        <v>2.277999999999999</v>
+      </c>
+      <c r="E29">
+        <v>5.189283999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>14.814</v>
+      </c>
+      <c r="C30">
+        <v>14.963</v>
+      </c>
+      <c r="D30">
+        <v>0.1489999999999991</v>
+      </c>
+      <c r="E30">
+        <v>0.02220099999999974</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14.322</v>
+      </c>
+      <c r="C31">
+        <v>12.401</v>
+      </c>
+      <c r="D31">
+        <v>1.920999999999999</v>
+      </c>
+      <c r="E31">
+        <v>3.690240999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>11.558</v>
+      </c>
+      <c r="C2">
+        <v>14.235</v>
+      </c>
+      <c r="D2">
+        <v>2.677</v>
+      </c>
+      <c r="E2">
+        <v>7.166328999999998</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>14.717</v>
+      </c>
+      <c r="C3">
+        <v>13.688</v>
+      </c>
+      <c r="D3">
+        <v>1.029</v>
+      </c>
+      <c r="E3">
+        <v>1.058841</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>14.867</v>
+      </c>
+      <c r="C4">
+        <v>13.673</v>
+      </c>
+      <c r="D4">
+        <v>1.194000000000001</v>
+      </c>
+      <c r="E4">
+        <v>1.425636000000002</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7.647</v>
+      </c>
+      <c r="C5">
+        <v>8.272</v>
+      </c>
+      <c r="D5">
+        <v>0.625</v>
+      </c>
+      <c r="E5">
+        <v>0.390625</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>1.790265130269093</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6.245</v>
+      </c>
+      <c r="C6">
+        <v>7.694</v>
+      </c>
+      <c r="D6">
+        <v>1.449</v>
+      </c>
+      <c r="E6">
+        <v>2.099600999999999</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>1.478343441032465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14.514</v>
+      </c>
+      <c r="C7">
+        <v>14.272</v>
+      </c>
+      <c r="D7">
+        <v>0.2419999999999991</v>
+      </c>
+      <c r="E7">
+        <v>0.05856399999999957</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.6881575307261216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>13.608</v>
+      </c>
+      <c r="C8">
+        <v>15.148</v>
+      </c>
+      <c r="D8">
+        <v>1.539999999999999</v>
+      </c>
+      <c r="E8">
+        <v>2.371599999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.168</v>
+      </c>
+      <c r="C9">
+        <v>9.493</v>
+      </c>
+      <c r="D9">
+        <v>0.6749999999999989</v>
+      </c>
+      <c r="E9">
+        <v>0.4556249999999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>10.325</v>
+      </c>
+      <c r="C10">
+        <v>14.117</v>
+      </c>
+      <c r="D10">
+        <v>3.792000000000002</v>
+      </c>
+      <c r="E10">
+        <v>14.37926400000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>15.851</v>
+      </c>
+      <c r="C11">
+        <v>13.578</v>
+      </c>
+      <c r="D11">
+        <v>2.273000000000001</v>
+      </c>
+      <c r="E11">
+        <v>5.166529000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C12">
+        <v>9.375</v>
+      </c>
+      <c r="D12">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="E12">
+        <v>0.1122250000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>14.514</v>
+      </c>
+      <c r="C13">
+        <v>15.117</v>
+      </c>
+      <c r="D13">
+        <v>0.6030000000000015</v>
+      </c>
+      <c r="E13">
+        <v>0.3636090000000018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>16.24</v>
+      </c>
+      <c r="C14">
+        <v>13.54</v>
+      </c>
+      <c r="D14">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="E14">
+        <v>7.289999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.728</v>
+      </c>
+      <c r="C15">
+        <v>14.368</v>
+      </c>
+      <c r="D15">
+        <v>2.640000000000001</v>
+      </c>
+      <c r="E15">
+        <v>6.969600000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>12.485</v>
+      </c>
+      <c r="C16">
+        <v>13.902</v>
+      </c>
+      <c r="D16">
+        <v>1.417</v>
+      </c>
+      <c r="E16">
+        <v>2.007889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>10.008</v>
+      </c>
+      <c r="C17">
+        <v>9.493</v>
+      </c>
+      <c r="D17">
+        <v>0.5149999999999988</v>
+      </c>
+      <c r="E17">
+        <v>0.2652249999999988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>12.512</v>
+      </c>
+      <c r="C18">
+        <v>12.996</v>
+      </c>
+      <c r="D18">
+        <v>0.484</v>
+      </c>
+      <c r="E18">
+        <v>0.234256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>6.301</v>
+      </c>
+      <c r="C19">
+        <v>6.795</v>
+      </c>
+      <c r="D19">
+        <v>0.4939999999999998</v>
+      </c>
+      <c r="E19">
+        <v>0.2440359999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.577</v>
+      </c>
+      <c r="C20">
+        <v>11.168</v>
+      </c>
+      <c r="D20">
+        <v>1.590999999999999</v>
+      </c>
+      <c r="E20">
+        <v>2.531280999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>12.629</v>
+      </c>
+      <c r="C21">
+        <v>10.99</v>
+      </c>
+      <c r="D21">
+        <v>1.638999999999999</v>
+      </c>
+      <c r="E21">
+        <v>2.686320999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>10.389</v>
+      </c>
+      <c r="C22">
+        <v>11.5</v>
+      </c>
+      <c r="D22">
+        <v>1.111000000000001</v>
+      </c>
+      <c r="E22">
+        <v>1.234321000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>12.196</v>
+      </c>
+      <c r="C23">
+        <v>13.377</v>
+      </c>
+      <c r="D23">
+        <v>1.181000000000001</v>
+      </c>
+      <c r="E23">
+        <v>1.394761000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7.545</v>
+      </c>
+      <c r="C24">
+        <v>8.18</v>
+      </c>
+      <c r="D24">
+        <v>0.6349999999999998</v>
+      </c>
+      <c r="E24">
+        <v>0.4032249999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6.753</v>
+      </c>
+      <c r="C25">
+        <v>8.361000000000001</v>
+      </c>
+      <c r="D25">
+        <v>1.608000000000001</v>
+      </c>
+      <c r="E25">
+        <v>2.585664000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>13.289</v>
+      </c>
+      <c r="C26">
+        <v>11.636</v>
+      </c>
+      <c r="D26">
+        <v>1.653</v>
+      </c>
+      <c r="E26">
+        <v>2.732409000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>9.148999999999999</v>
+      </c>
+      <c r="C27">
+        <v>10.638</v>
+      </c>
+      <c r="D27">
+        <v>1.489000000000001</v>
+      </c>
+      <c r="E27">
+        <v>2.217121000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>18.214</v>
+      </c>
+      <c r="C28">
+        <v>13.806</v>
+      </c>
+      <c r="D28">
+        <v>4.407999999999999</v>
+      </c>
+      <c r="E28">
+        <v>19.430464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>16.758</v>
+      </c>
+      <c r="C29">
+        <v>14.484</v>
+      </c>
+      <c r="D29">
+        <v>2.273999999999999</v>
+      </c>
+      <c r="E29">
+        <v>5.171075999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>14.814</v>
+      </c>
+      <c r="C30">
+        <v>14.973</v>
+      </c>
+      <c r="D30">
+        <v>0.1590000000000007</v>
+      </c>
+      <c r="E30">
+        <v>0.02528100000000022</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14.322</v>
+      </c>
+      <c r="C31">
+        <v>12.404</v>
+      </c>
+      <c r="D31">
+        <v>1.917999999999999</v>
+      </c>
+      <c r="E31">
+        <v>3.678723999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>11.558</v>
+      </c>
+      <c r="C2">
+        <v>14.274</v>
+      </c>
+      <c r="D2">
+        <v>2.715999999999999</v>
+      </c>
+      <c r="E2">
+        <v>7.376655999999996</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>14.717</v>
+      </c>
+      <c r="C3">
+        <v>13.706</v>
+      </c>
+      <c r="D3">
+        <v>1.011000000000001</v>
+      </c>
+      <c r="E3">
+        <v>1.022121000000002</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>14.867</v>
+      </c>
+      <c r="C4">
+        <v>13.692</v>
+      </c>
+      <c r="D4">
+        <v>1.175000000000001</v>
+      </c>
+      <c r="E4">
+        <v>1.380625000000002</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7.647</v>
+      </c>
+      <c r="C5">
+        <v>8.268000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.6210000000000004</v>
+      </c>
+      <c r="E5">
+        <v>0.3856410000000006</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>1.792050797445763</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6.245</v>
+      </c>
+      <c r="C6">
+        <v>7.692</v>
+      </c>
+      <c r="D6">
+        <v>1.447</v>
+      </c>
+      <c r="E6">
+        <v>2.093809</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>1.483269850966529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14.514</v>
+      </c>
+      <c r="C7">
+        <v>14.275</v>
+      </c>
+      <c r="D7">
+        <v>0.238999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.05712099999999952</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.6875351373603481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>13.608</v>
+      </c>
+      <c r="C8">
+        <v>15.17</v>
+      </c>
+      <c r="D8">
+        <v>1.561999999999999</v>
+      </c>
+      <c r="E8">
+        <v>2.439843999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.168</v>
+      </c>
+      <c r="C9">
+        <v>9.465</v>
+      </c>
+      <c r="D9">
+        <v>0.7029999999999994</v>
+      </c>
+      <c r="E9">
+        <v>0.4942089999999992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>10.325</v>
+      </c>
+      <c r="C10">
+        <v>14.14</v>
+      </c>
+      <c r="D10">
+        <v>3.815000000000001</v>
+      </c>
+      <c r="E10">
+        <v>14.55422500000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>15.851</v>
+      </c>
+      <c r="C11">
+        <v>13.596</v>
+      </c>
+      <c r="D11">
+        <v>2.255000000000001</v>
+      </c>
+      <c r="E11">
+        <v>5.085025000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C12">
+        <v>9.375999999999999</v>
+      </c>
+      <c r="D12">
+        <v>0.3360000000000003</v>
+      </c>
+      <c r="E12">
+        <v>0.1128960000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>14.514</v>
+      </c>
+      <c r="C13">
+        <v>15.136</v>
+      </c>
+      <c r="D13">
+        <v>0.6219999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.3868839999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>16.24</v>
+      </c>
+      <c r="C14">
+        <v>13.557</v>
+      </c>
+      <c r="D14">
+        <v>2.682999999999998</v>
+      </c>
+      <c r="E14">
+        <v>7.19848899999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.728</v>
+      </c>
+      <c r="C15">
+        <v>14.389</v>
+      </c>
+      <c r="D15">
+        <v>2.661</v>
+      </c>
+      <c r="E15">
+        <v>7.080920999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>12.485</v>
+      </c>
+      <c r="C16">
+        <v>13.922</v>
+      </c>
+      <c r="D16">
+        <v>1.437000000000001</v>
+      </c>
+      <c r="E16">
+        <v>2.064969000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>10.008</v>
+      </c>
+      <c r="C17">
+        <v>9.487</v>
+      </c>
+      <c r="D17">
+        <v>0.520999999999999</v>
+      </c>
+      <c r="E17">
+        <v>0.271440999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>12.512</v>
+      </c>
+      <c r="C18">
+        <v>13.057</v>
+      </c>
+      <c r="D18">
+        <v>0.5449999999999999</v>
+      </c>
+      <c r="E18">
+        <v>0.2970249999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>6.301</v>
+      </c>
+      <c r="C19">
+        <v>6.777</v>
+      </c>
+      <c r="D19">
+        <v>0.476</v>
+      </c>
+      <c r="E19">
+        <v>0.226576</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.577</v>
+      </c>
+      <c r="C20">
+        <v>11.148</v>
+      </c>
+      <c r="D20">
+        <v>1.571</v>
+      </c>
+      <c r="E20">
+        <v>2.468040999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>12.629</v>
+      </c>
+      <c r="C21">
+        <v>10.988</v>
+      </c>
+      <c r="D21">
+        <v>1.641</v>
+      </c>
+      <c r="E21">
+        <v>2.692881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>10.389</v>
+      </c>
+      <c r="C22">
+        <v>11.44</v>
+      </c>
+      <c r="D22">
+        <v>1.051</v>
+      </c>
+      <c r="E22">
+        <v>1.104601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>12.196</v>
+      </c>
+      <c r="C23">
+        <v>13.393</v>
+      </c>
+      <c r="D23">
+        <v>1.197000000000001</v>
+      </c>
+      <c r="E23">
+        <v>1.432809000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7.545</v>
+      </c>
+      <c r="C24">
+        <v>8.295</v>
+      </c>
+      <c r="D24">
+        <v>0.75</v>
+      </c>
+      <c r="E24">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6.753</v>
+      </c>
+      <c r="C25">
+        <v>8.339</v>
+      </c>
+      <c r="D25">
+        <v>1.586</v>
+      </c>
+      <c r="E25">
+        <v>2.515396000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>13.289</v>
+      </c>
+      <c r="C26">
+        <v>11.626</v>
+      </c>
+      <c r="D26">
+        <v>1.663</v>
+      </c>
+      <c r="E26">
+        <v>2.765569000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>9.148999999999999</v>
+      </c>
+      <c r="C27">
+        <v>10.617</v>
+      </c>
+      <c r="D27">
+        <v>1.468000000000002</v>
+      </c>
+      <c r="E27">
+        <v>2.155024000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>18.214</v>
+      </c>
+      <c r="C28">
+        <v>13.822</v>
+      </c>
+      <c r="D28">
+        <v>4.391999999999999</v>
+      </c>
+      <c r="E28">
+        <v>19.28966399999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>16.758</v>
+      </c>
+      <c r="C29">
+        <v>14.489</v>
+      </c>
+      <c r="D29">
+        <v>2.268999999999998</v>
+      </c>
+      <c r="E29">
+        <v>5.148360999999992</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>14.814</v>
+      </c>
+      <c r="C30">
+        <v>14.989</v>
+      </c>
+      <c r="D30">
+        <v>0.1750000000000007</v>
+      </c>
+      <c r="E30">
+        <v>0.03062500000000025</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14.322</v>
+      </c>
+      <c r="C31">
+        <v>12.411</v>
+      </c>
+      <c r="D31">
+        <v>1.911</v>
+      </c>
+      <c r="E31">
+        <v>3.651920999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>11.558</v>
+      </c>
+      <c r="C2">
+        <v>14.265</v>
+      </c>
+      <c r="D2">
+        <v>2.707000000000001</v>
+      </c>
+      <c r="E2">
+        <v>7.327849000000004</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>14.717</v>
+      </c>
+      <c r="C3">
+        <v>13.646</v>
+      </c>
+      <c r="D3">
+        <v>1.071</v>
+      </c>
+      <c r="E3">
+        <v>1.147040999999999</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>14.867</v>
+      </c>
+      <c r="C4">
+        <v>13.632</v>
+      </c>
+      <c r="D4">
+        <v>1.235000000000001</v>
+      </c>
+      <c r="E4">
+        <v>1.525225000000003</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7.647</v>
+      </c>
+      <c r="C5">
+        <v>8.287000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="E5">
+        <v>0.4096000000000007</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>1.799723775698587</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6.245</v>
+      </c>
+      <c r="C6">
+        <v>7.695</v>
+      </c>
+      <c r="D6">
+        <v>1.45</v>
+      </c>
+      <c r="E6">
+        <v>2.1025</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>1.492751417610956</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>14.514</v>
+      </c>
+      <c r="C7">
+        <v>14.406</v>
+      </c>
+      <c r="D7">
+        <v>0.1079999999999988</v>
+      </c>
+      <c r="E7">
+        <v>0.01166399999999973</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>0.6848536633375735</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>13.608</v>
+      </c>
+      <c r="C8">
+        <v>15.097</v>
+      </c>
+      <c r="D8">
+        <v>1.488999999999999</v>
+      </c>
+      <c r="E8">
+        <v>2.217120999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10.168</v>
+      </c>
+      <c r="C9">
+        <v>9.204000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.9639999999999986</v>
+      </c>
+      <c r="E9">
+        <v>0.9292959999999973</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>10.325</v>
+      </c>
+      <c r="C10">
+        <v>14.064</v>
+      </c>
+      <c r="D10">
+        <v>3.739000000000001</v>
+      </c>
+      <c r="E10">
+        <v>13.98012100000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>15.851</v>
+      </c>
+      <c r="C11">
+        <v>13.538</v>
+      </c>
+      <c r="D11">
+        <v>2.313000000000001</v>
+      </c>
+      <c r="E11">
+        <v>5.349969000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C12">
+        <v>9.356</v>
+      </c>
+      <c r="D12">
+        <v>0.3160000000000007</v>
+      </c>
+      <c r="E12">
+        <v>0.09985600000000046</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>14.514</v>
+      </c>
+      <c r="C13">
+        <v>15.074</v>
+      </c>
+      <c r="D13">
+        <v>0.5600000000000005</v>
+      </c>
+      <c r="E13">
+        <v>0.3136000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>16.24</v>
+      </c>
+      <c r="C14">
+        <v>13.501</v>
+      </c>
+      <c r="D14">
+        <v>2.738999999999999</v>
+      </c>
+      <c r="E14">
+        <v>7.502120999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>11.728</v>
+      </c>
+      <c r="C15">
+        <v>14.321</v>
+      </c>
+      <c r="D15">
+        <v>2.593</v>
+      </c>
+      <c r="E15">
+        <v>6.723649</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>12.485</v>
+      </c>
+      <c r="C16">
+        <v>13.857</v>
+      </c>
+      <c r="D16">
+        <v>1.372</v>
+      </c>
+      <c r="E16">
+        <v>1.882384</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>10.008</v>
+      </c>
+      <c r="C17">
+        <v>9.385</v>
+      </c>
+      <c r="D17">
+        <v>0.6229999999999993</v>
+      </c>
+      <c r="E17">
+        <v>0.3881289999999992</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>12.512</v>
+      </c>
+      <c r="C18">
+        <v>13.006</v>
+      </c>
+      <c r="D18">
+        <v>0.4939999999999998</v>
+      </c>
+      <c r="E18">
+        <v>0.2440359999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>6.301</v>
+      </c>
+      <c r="C19">
+        <v>6.666</v>
+      </c>
+      <c r="D19">
+        <v>0.3650000000000002</v>
+      </c>
+      <c r="E19">
+        <v>0.1332250000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>9.577</v>
+      </c>
+      <c r="C20">
+        <v>11.213</v>
+      </c>
+      <c r="D20">
+        <v>1.635999999999999</v>
+      </c>
+      <c r="E20">
+        <v>2.676495999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>12.629</v>
+      </c>
+      <c r="C21">
+        <v>10.996</v>
+      </c>
+      <c r="D21">
+        <v>1.632999999999999</v>
+      </c>
+      <c r="E21">
+        <v>2.666688999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>10.389</v>
+      </c>
+      <c r="C22">
+        <v>11.642</v>
+      </c>
+      <c r="D22">
+        <v>1.253</v>
+      </c>
+      <c r="E22">
+        <v>1.570009</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>12.196</v>
+      </c>
+      <c r="C23">
+        <v>13.343</v>
+      </c>
+      <c r="D23">
+        <v>1.147</v>
+      </c>
+      <c r="E23">
+        <v>1.315609</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7.545</v>
+      </c>
+      <c r="C24">
+        <v>8.378</v>
+      </c>
+      <c r="D24">
+        <v>0.8330000000000002</v>
+      </c>
+      <c r="E24">
+        <v>0.6938890000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6.753</v>
+      </c>
+      <c r="C25">
+        <v>8.420999999999999</v>
+      </c>
+      <c r="D25">
+        <v>1.667999999999999</v>
+      </c>
+      <c r="E25">
+        <v>2.782223999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>13.289</v>
+      </c>
+      <c r="C26">
+        <v>11.652</v>
+      </c>
+      <c r="D26">
+        <v>1.637</v>
+      </c>
+      <c r="E26">
+        <v>2.679769000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>9.148999999999999</v>
+      </c>
+      <c r="C27">
+        <v>10.687</v>
+      </c>
+      <c r="D27">
+        <v>1.538</v>
+      </c>
+      <c r="E27">
+        <v>2.365444000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>18.214</v>
+      </c>
+      <c r="C28">
+        <v>13.776</v>
+      </c>
+      <c r="D28">
+        <v>4.437999999999999</v>
+      </c>
+      <c r="E28">
+        <v>19.69584399999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>16.758</v>
+      </c>
+      <c r="C29">
+        <v>14.595</v>
+      </c>
+      <c r="D29">
+        <v>2.162999999999998</v>
+      </c>
+      <c r="E29">
+        <v>4.678568999999993</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>14.814</v>
+      </c>
+      <c r="C30">
+        <v>14.939</v>
+      </c>
+      <c r="D30">
+        <v>0.125</v>
+      </c>
+      <c r="E30">
+        <v>0.015625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14.322</v>
+      </c>
+      <c r="C31">
+        <v>12.389</v>
+      </c>
+      <c r="D31">
+        <v>1.933</v>
+      </c>
+      <c r="E31">
+        <v>3.736488999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F253"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0.95</v>
+      </c>
+      <c r="D2">
+        <v>0.6911800473958375</v>
+      </c>
+      <c r="E2">
+        <v>1.781567979657713</v>
+      </c>
+      <c r="F2">
+        <v>1.47874368993348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>0.9</v>
+      </c>
+      <c r="D3">
+        <v>0.6881899947750428</v>
+      </c>
+      <c r="E3">
+        <v>1.79017194096169</v>
+      </c>
+      <c r="F3">
+        <v>1.464022474616932</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>0.88</v>
+      </c>
+      <c r="D4">
+        <v>0.6881575307261216</v>
+      </c>
+      <c r="E4">
+        <v>1.790265130269093</v>
+      </c>
+      <c r="F4">
+        <v>1.478343441032465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>0.85</v>
+      </c>
+      <c r="D5">
+        <v>0.6875351373603481</v>
+      </c>
+      <c r="E5">
+        <v>1.792050797445763</v>
+      </c>
+      <c r="F5">
+        <v>1.483269850966529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>0.95</v>
+      </c>
+      <c r="D6">
+        <v>0.6848536633375735</v>
+      </c>
+      <c r="E6">
+        <v>1.799723775698587</v>
+      </c>
+      <c r="F6">
+        <v>1.492751417610956</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>1.1</v>
+      </c>
+      <c r="D7">
+        <v>0.679972658130523</v>
+      </c>
+      <c r="E7">
+        <v>1.813607339329162</v>
+      </c>
+      <c r="F7">
+        <v>1.512745441187314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>0.82</v>
+      </c>
+      <c r="D8">
+        <v>0.6774715952184043</v>
+      </c>
+      <c r="E8">
+        <v>1.820680357231072</v>
+      </c>
+      <c r="F8">
+        <v>1.506134984948541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>0.7</v>
+      </c>
+      <c r="D9">
+        <v>0.6749033414883145</v>
+      </c>
+      <c r="E9">
+        <v>1.827914909888804</v>
+      </c>
+      <c r="F9">
+        <v>1.513512452945867</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0.6744355691154105</v>
+      </c>
+      <c r="E10">
+        <v>1.829229504667693</v>
+      </c>
+      <c r="F10">
+        <v>1.529051376800728</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>0.88</v>
+      </c>
+      <c r="D11">
+        <v>0.6742751319682714</v>
+      </c>
+      <c r="E11">
+        <v>1.829680168481363</v>
+      </c>
+      <c r="F11">
+        <v>1.511864020160254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>0.77</v>
+      </c>
+      <c r="D12">
+        <v>0.6741649852112588</v>
+      </c>
+      <c r="E12">
+        <v>1.829989503631999</v>
+      </c>
+      <c r="F12">
+        <v>1.545048750462997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>0.82</v>
+      </c>
+      <c r="D13">
+        <v>0.6716497732650035</v>
+      </c>
+      <c r="E13">
+        <v>1.837039026815869</v>
+      </c>
+      <c r="F13">
+        <v>1.518656251423068</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>0.8</v>
+      </c>
+      <c r="D14">
+        <v>0.6715277562196971</v>
+      </c>
+      <c r="E14">
+        <v>1.837380322840485</v>
+      </c>
+      <c r="F14">
+        <v>1.529737462534274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>0.8</v>
+      </c>
+      <c r="D15">
+        <v>0.6707118002425343</v>
+      </c>
+      <c r="E15">
+        <v>1.839661020202167</v>
+      </c>
+      <c r="F15">
+        <v>1.513622248550158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>1.05</v>
+      </c>
+      <c r="D16">
+        <v>0.6706162001012005</v>
+      </c>
+      <c r="E16">
+        <v>1.83992804934348</v>
+      </c>
+      <c r="F16">
+        <v>1.539431196624115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1.05</v>
+      </c>
+      <c r="D17">
+        <v>0.6697874755911672</v>
+      </c>
+      <c r="E17">
+        <v>1.842241210444806</v>
+      </c>
+      <c r="F17">
+        <v>1.535302736094377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>0.85</v>
+      </c>
+      <c r="D18">
+        <v>0.6697001755793872</v>
+      </c>
+      <c r="E18">
+        <v>1.842484715822672</v>
+      </c>
+      <c r="F18">
+        <v>1.524481692508318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>0.77</v>
+      </c>
+      <c r="D19">
+        <v>0.6696274773495734</v>
+      </c>
+      <c r="E19">
+        <v>1.84268746798592</v>
+      </c>
+      <c r="F19">
+        <v>1.507329822582998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>1.1</v>
+      </c>
+      <c r="D20">
+        <v>0.6681816524636057</v>
+      </c>
+      <c r="E20">
+        <v>1.846715186253709</v>
+      </c>
+      <c r="F20">
+        <v>1.54961473838981</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>0.88</v>
+      </c>
+      <c r="D21">
+        <v>0.6675699174466723</v>
+      </c>
+      <c r="E21">
+        <v>1.848416689740679</v>
+      </c>
+      <c r="F21">
+        <v>1.530389827341764</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0.6664712270258581</v>
+      </c>
+      <c r="E22">
+        <v>1.851468703669287</v>
+      </c>
+      <c r="F22">
+        <v>1.5503528486771</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>0.9</v>
+      </c>
+      <c r="D23">
+        <v>0.6660508174623819</v>
+      </c>
+      <c r="E23">
+        <v>1.852635214752536</v>
+      </c>
+      <c r="F23">
+        <v>1.534501266720456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>0.75</v>
+      </c>
+      <c r="D24">
+        <v>0.6657793869887212</v>
+      </c>
+      <c r="E24">
+        <v>1.853387963286527</v>
+      </c>
+      <c r="F24">
+        <v>1.529067087684087</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>0.7</v>
+      </c>
+      <c r="D25">
+        <v>0.6636021486840167</v>
+      </c>
+      <c r="E25">
+        <v>1.859414995459923</v>
+      </c>
+      <c r="F25">
+        <v>1.576226864694384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>0.95</v>
+      </c>
+      <c r="D26">
+        <v>0.6625415214728583</v>
+      </c>
+      <c r="E26">
+        <v>1.862343959016742</v>
+      </c>
+      <c r="F26">
+        <v>1.53997408571734</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>0.75</v>
+      </c>
+      <c r="D27">
+        <v>0.6623812150249671</v>
+      </c>
+      <c r="E27">
+        <v>1.862786250908789</v>
+      </c>
+      <c r="F27">
+        <v>1.576011332174278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0.6623345231226729</v>
+      </c>
+      <c r="E28">
+        <v>1.862915055984987</v>
+      </c>
+      <c r="F28">
+        <v>1.54386669334119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>0.77</v>
+      </c>
+      <c r="D29">
+        <v>0.6620246968666397</v>
+      </c>
+      <c r="E29">
+        <v>1.863769522459788</v>
+      </c>
+      <c r="F29">
+        <v>1.542176494505846</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>0.82</v>
+      </c>
+      <c r="D30">
+        <v>0.66185980400553</v>
+      </c>
+      <c r="E30">
+        <v>1.864224119009989</v>
+      </c>
+      <c r="F30">
+        <v>1.586331316294569</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>0.88</v>
+      </c>
+      <c r="D31">
+        <v>0.6617521142743219</v>
+      </c>
+      <c r="E31">
+        <v>1.864520951233793</v>
+      </c>
+      <c r="F31">
+        <v>1.57568777751501</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>0.8</v>
+      </c>
+      <c r="D32">
+        <v>0.6611794788904779</v>
+      </c>
+      <c r="E32">
+        <v>1.866098550403059</v>
+      </c>
+      <c r="F32">
+        <v>1.577245099732288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>0.9</v>
+      </c>
+      <c r="D33">
+        <v>0.661105766602485</v>
+      </c>
+      <c r="E33">
+        <v>1.866301529420834</v>
+      </c>
+      <c r="F33">
+        <v>1.548275439216433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>0.85</v>
+      </c>
+      <c r="D34">
+        <v>0.660634626718087</v>
+      </c>
+      <c r="E34">
+        <v>1.867598370159929</v>
+      </c>
+      <c r="F34">
+        <v>1.585303065831173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>1.1</v>
+      </c>
+      <c r="D35">
+        <v>0.6601843780203758</v>
+      </c>
+      <c r="E35">
+        <v>1.868836865712371</v>
+      </c>
+      <c r="F35">
+        <v>1.549251064486166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>0.82</v>
+      </c>
+      <c r="D36">
+        <v>0.6586014862565108</v>
+      </c>
+      <c r="E36">
+        <v>1.873184413971049</v>
+      </c>
+      <c r="F36">
+        <v>1.582770070506856</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37">
+        <v>0.77</v>
+      </c>
+      <c r="D37">
+        <v>0.6571915382949041</v>
+      </c>
+      <c r="E37">
+        <v>1.877048477788373</v>
+      </c>
+      <c r="F37">
+        <v>1.598174799950561</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38">
+        <v>1.05</v>
+      </c>
+      <c r="D38">
+        <v>0.6540729762362638</v>
+      </c>
+      <c r="E38">
+        <v>1.88556699487214</v>
+      </c>
+      <c r="F38">
+        <v>1.571102249852207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39">
+        <v>0.8</v>
+      </c>
+      <c r="D39">
+        <v>0.6536233650048366</v>
+      </c>
+      <c r="E39">
+        <v>1.886791959605673</v>
+      </c>
+      <c r="F39">
+        <v>1.608587424191046</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40">
+        <v>1.1</v>
+      </c>
+      <c r="D40">
+        <v>0.6533546526284534</v>
+      </c>
+      <c r="E40">
+        <v>1.887523686297146</v>
+      </c>
+      <c r="F40">
+        <v>1.596142517475456</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>1.1</v>
+      </c>
+      <c r="D41">
+        <v>0.6518819012222882</v>
+      </c>
+      <c r="E41">
+        <v>1.8915290866737</v>
+      </c>
+      <c r="F41">
+        <v>1.577758106731557</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>0.6503511187472706</v>
+      </c>
+      <c r="E42">
+        <v>1.89568334272019</v>
+      </c>
+      <c r="F42">
+        <v>1.573006360707554</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>0.75</v>
+      </c>
+      <c r="D43">
+        <v>0.6497018792841276</v>
+      </c>
+      <c r="E43">
+        <v>1.897442509853503</v>
+      </c>
+      <c r="F43">
+        <v>1.594548155198537</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44">
+        <v>0.95</v>
+      </c>
+      <c r="D44">
+        <v>0.6493077932348905</v>
+      </c>
+      <c r="E44">
+        <v>1.898509523048474</v>
+      </c>
+      <c r="F44">
+        <v>1.566705331007455</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>0.75</v>
+      </c>
+      <c r="D45">
+        <v>0.6488461580889205</v>
+      </c>
+      <c r="E45">
+        <v>1.89975866756069</v>
+      </c>
+      <c r="F45">
+        <v>1.566463226238018</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46">
+        <v>0.95</v>
+      </c>
+      <c r="D46">
+        <v>0.6480853122565283</v>
+      </c>
+      <c r="E46">
+        <v>1.901815659666179</v>
+      </c>
+      <c r="F46">
+        <v>1.60456904363875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47">
+        <v>0.9</v>
+      </c>
+      <c r="D47">
+        <v>0.64779028050696</v>
+      </c>
+      <c r="E47">
+        <v>1.902612697229408</v>
+      </c>
+      <c r="F47">
+        <v>1.616686859671685</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48">
+        <v>0.7</v>
+      </c>
+      <c r="D48">
+        <v>0.6467245605011759</v>
+      </c>
+      <c r="E48">
+        <v>1.905488996200617</v>
+      </c>
+      <c r="F48">
+        <v>1.620693572584043</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49">
+        <v>0.85</v>
+      </c>
+      <c r="D49">
+        <v>0.6465275590264938</v>
+      </c>
+      <c r="E49">
+        <v>1.906020213180777</v>
+      </c>
+      <c r="F49">
+        <v>1.618899128446694</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <v>1.05</v>
+      </c>
+      <c r="D50">
+        <v>0.6451005151548035</v>
+      </c>
+      <c r="E50">
+        <v>1.909863843401332</v>
+      </c>
+      <c r="F50">
+        <v>1.582858046578071</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>1.05</v>
+      </c>
+      <c r="D51">
+        <v>0.6447047577530876</v>
+      </c>
+      <c r="E51">
+        <v>1.910928415466268</v>
+      </c>
+      <c r="F51">
+        <v>1.618260266845685</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>0.6432651141312111</v>
+      </c>
+      <c r="E52">
+        <v>1.914796008407421</v>
+      </c>
+      <c r="F52">
+        <v>1.60919122453693</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>1.05</v>
+      </c>
+      <c r="D53">
+        <v>0.6425362922150819</v>
+      </c>
+      <c r="E53">
+        <v>1.916751008172323</v>
+      </c>
+      <c r="F53">
+        <v>1.624846238281502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>1.1</v>
+      </c>
+      <c r="D54">
+        <v>0.641911734948451</v>
+      </c>
+      <c r="E54">
+        <v>1.918424742178253</v>
+      </c>
+      <c r="F54">
+        <v>1.599721857792574</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55">
+        <v>1.1</v>
+      </c>
+      <c r="D55">
+        <v>0.6415105680731439</v>
+      </c>
+      <c r="E55">
+        <v>1.91949904858071</v>
+      </c>
+      <c r="F55">
+        <v>1.628067807609472</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>0.6402310542703398</v>
+      </c>
+      <c r="E56">
+        <v>1.922921517572372</v>
+      </c>
+      <c r="F56">
+        <v>1.637749863753017</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57">
+        <v>0.9</v>
+      </c>
+      <c r="D57">
+        <v>0.6398727936111492</v>
+      </c>
+      <c r="E57">
+        <v>1.923878709291152</v>
+      </c>
+      <c r="F57">
+        <v>1.65611570241312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58">
+        <v>1.05</v>
+      </c>
+      <c r="D58">
+        <v>0.6393982964623441</v>
+      </c>
+      <c r="E58">
+        <v>1.925145726121635</v>
+      </c>
+      <c r="F58">
+        <v>1.617499649805657</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59">
+        <v>0.88</v>
+      </c>
+      <c r="D59">
+        <v>0.6387635613157823</v>
+      </c>
+      <c r="E59">
+        <v>1.926839312687502</v>
+      </c>
+      <c r="F59">
+        <v>1.6157506309796</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>0.6374372020323142</v>
+      </c>
+      <c r="E60">
+        <v>1.930373479367274</v>
+      </c>
+      <c r="F60">
+        <v>1.63923173476184</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>0.9</v>
+      </c>
+      <c r="D61">
+        <v>0.6363373731364113</v>
+      </c>
+      <c r="E61">
+        <v>1.933299142036585</v>
+      </c>
+      <c r="F61">
+        <v>1.613256285212609</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62">
+        <v>0.95</v>
+      </c>
+      <c r="D62">
+        <v>0.6351747931843654</v>
+      </c>
+      <c r="E62">
+        <v>1.936386923394651</v>
+      </c>
+      <c r="F62">
+        <v>1.649243101201776</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>26</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63">
+        <v>0.88</v>
+      </c>
+      <c r="D63">
+        <v>0.6340980386374598</v>
+      </c>
+      <c r="E63">
+        <v>1.939242369250498</v>
+      </c>
+      <c r="F63">
+        <v>1.672790682237687</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64">
+        <v>0.82</v>
+      </c>
+      <c r="D64">
+        <v>0.6300247204206559</v>
+      </c>
+      <c r="E64">
+        <v>1.950006576274446</v>
+      </c>
+      <c r="F64">
+        <v>1.670275601021162</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65">
+        <v>0.8</v>
+      </c>
+      <c r="D65">
+        <v>0.6300038519643549</v>
+      </c>
+      <c r="E65">
+        <v>1.950061570561166</v>
+      </c>
+      <c r="F65">
+        <v>1.628361907912907</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>0.75</v>
+      </c>
+      <c r="D66">
+        <v>0.6277936927401739</v>
+      </c>
+      <c r="E66">
+        <v>1.955877211363901</v>
+      </c>
+      <c r="F66">
+        <v>1.683820121047957</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67">
+        <v>0.85</v>
+      </c>
+      <c r="D67">
+        <v>0.6270317139216544</v>
+      </c>
+      <c r="E67">
+        <v>1.957878218607519</v>
+      </c>
+      <c r="F67">
+        <v>1.671633922322638</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68">
+        <v>0.85</v>
+      </c>
+      <c r="D68">
+        <v>0.6266728293836552</v>
+      </c>
+      <c r="E68">
+        <v>1.958819965262182</v>
+      </c>
+      <c r="F68">
+        <v>1.646837764324518</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69">
+        <v>0.8</v>
+      </c>
+      <c r="D69">
+        <v>0.6263054347593836</v>
+      </c>
+      <c r="E69">
+        <v>1.959783574413751</v>
+      </c>
+      <c r="F69">
+        <v>1.673551182989638</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70">
+        <v>0.82</v>
+      </c>
+      <c r="D70">
+        <v>0.6234487042675838</v>
+      </c>
+      <c r="E70">
+        <v>1.967260154299069</v>
+      </c>
+      <c r="F70">
+        <v>1.655604120164386</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71">
+        <v>0.7</v>
+      </c>
+      <c r="D71">
+        <v>0.6233405334872154</v>
+      </c>
+      <c r="E71">
+        <v>1.967542698520895</v>
+      </c>
+      <c r="F71">
+        <v>1.660941355024634</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>0.77</v>
+      </c>
+      <c r="D72">
+        <v>0.6216175702995913</v>
+      </c>
+      <c r="E72">
+        <v>1.972037654889601</v>
+      </c>
+      <c r="F72">
+        <v>1.6988284170574</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>0.7</v>
+      </c>
+      <c r="D73">
+        <v>0.6211380571200174</v>
+      </c>
+      <c r="E73">
+        <v>1.973286812584265</v>
+      </c>
+      <c r="F73">
+        <v>1.706397702107343</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74">
+        <v>0.77</v>
+      </c>
+      <c r="D74">
+        <v>0.6203829394090135</v>
+      </c>
+      <c r="E74">
+        <v>1.975252333427236</v>
+      </c>
+      <c r="F74">
+        <v>1.702411964701491</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75">
+        <v>0.95</v>
+      </c>
+      <c r="D75">
+        <v>0.6194129938496953</v>
+      </c>
+      <c r="E75">
+        <v>1.97777417080739</v>
+      </c>
+      <c r="F75">
+        <v>1.700187450978609</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76">
+        <v>0.82</v>
+      </c>
+      <c r="D76">
+        <v>0.6127203762395516</v>
+      </c>
+      <c r="E76">
+        <v>1.995087953541913</v>
+      </c>
+      <c r="F76">
+        <v>1.715012049017049</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77">
+        <v>0.8</v>
+      </c>
+      <c r="D77">
+        <v>0.6121803678513331</v>
+      </c>
+      <c r="E77">
+        <v>1.996478407449714</v>
+      </c>
+      <c r="F77">
+        <v>1.727215617102762</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78">
+        <v>0.77</v>
+      </c>
+      <c r="D78">
+        <v>0.6085830658317537</v>
+      </c>
+      <c r="E78">
+        <v>2.00571641092144</v>
+      </c>
+      <c r="F78">
+        <v>1.692193513209287</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79">
+        <v>0.75</v>
+      </c>
+      <c r="D79">
+        <v>0.6072952426212519</v>
+      </c>
+      <c r="E79">
+        <v>2.009013262417532</v>
+      </c>
+      <c r="F79">
+        <v>1.700150851712543</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>28</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80">
+        <v>0.85</v>
+      </c>
+      <c r="D80">
+        <v>0.6048964423403361</v>
+      </c>
+      <c r="E80">
+        <v>2.015139855536855</v>
+      </c>
+      <c r="F80">
+        <v>1.73182873329779</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81">
+        <v>0.9</v>
+      </c>
+      <c r="D81">
+        <v>0.6025515290876057</v>
+      </c>
+      <c r="E81">
+        <v>2.021110869545062</v>
+      </c>
+      <c r="F81">
+        <v>1.751026100482473</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82">
+        <v>0.9</v>
+      </c>
+      <c r="D82">
+        <v>0.6022571477605478</v>
+      </c>
+      <c r="E82">
+        <v>2.021859227146841</v>
+      </c>
+      <c r="F82">
+        <v>1.724827926307518</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>26</v>
+      </c>
+      <c r="B83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83">
+        <v>0.75</v>
+      </c>
+      <c r="D83">
+        <v>0.6017807059755267</v>
+      </c>
+      <c r="E83">
+        <v>2.023069820764602</v>
+      </c>
+      <c r="F83">
+        <v>1.764833251579859</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84">
+        <v>0.88</v>
+      </c>
+      <c r="D84">
+        <v>0.5990248626395486</v>
+      </c>
+      <c r="E84">
+        <v>2.03005799413268</v>
+      </c>
+      <c r="F84">
+        <v>1.716993657548069</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85">
+        <v>0.88</v>
+      </c>
+      <c r="D85">
+        <v>0.5990125688951464</v>
+      </c>
+      <c r="E85">
+        <v>2.030089114295111</v>
+      </c>
+      <c r="F85">
+        <v>1.760897340914912</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86">
+        <v>0.7</v>
+      </c>
+      <c r="D86">
+        <v>0.5938200074915677</v>
+      </c>
+      <c r="E86">
+        <v>2.0431910902852</v>
+      </c>
+      <c r="F86">
+        <v>1.753263129784258</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87">
+        <v>0.85</v>
+      </c>
+      <c r="D87">
+        <v>0.5934672690519506</v>
+      </c>
+      <c r="E87">
+        <v>2.044078080839184</v>
+      </c>
+      <c r="F87">
+        <v>1.773332702679259</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88">
+        <v>0.7</v>
+      </c>
+      <c r="D88">
+        <v>0.5926105189173982</v>
+      </c>
+      <c r="E88">
+        <v>2.046230850259897</v>
+      </c>
+      <c r="F88">
+        <v>1.74020489511387</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89">
+        <v>0.95</v>
+      </c>
+      <c r="D89">
+        <v>0.5907808792272558</v>
+      </c>
+      <c r="E89">
+        <v>2.050820648496963</v>
+      </c>
+      <c r="F89">
+        <v>1.749124101610016</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90">
+        <v>1.05</v>
+      </c>
+      <c r="D90">
+        <v>0.589344664649619</v>
+      </c>
+      <c r="E90">
+        <v>2.054416324435094</v>
+      </c>
+      <c r="F90">
+        <v>1.745610865402456</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0.5857135028182336</v>
+      </c>
+      <c r="E91">
+        <v>2.063479277223542</v>
+      </c>
+      <c r="F91">
+        <v>1.768706174383756</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>29</v>
+      </c>
+      <c r="B92" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92">
+        <v>0.8</v>
+      </c>
+      <c r="D92">
+        <v>0.5853861960594458</v>
+      </c>
+      <c r="E92">
+        <v>2.064294241473314</v>
+      </c>
+      <c r="F92">
+        <v>1.681668498701871</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>29</v>
+      </c>
+      <c r="B93" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93">
+        <v>0.82</v>
+      </c>
+      <c r="D93">
+        <v>0.5853104619599261</v>
+      </c>
+      <c r="E93">
+        <v>2.064482766705068</v>
+      </c>
+      <c r="F93">
+        <v>1.678572286890683</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>27</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94">
+        <v>0.8</v>
+      </c>
+      <c r="D94">
+        <v>0.5824603139437003</v>
+      </c>
+      <c r="E94">
+        <v>2.071565180465574</v>
+      </c>
+      <c r="F94">
+        <v>1.783351460941849</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>28</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95">
+        <v>1.1</v>
+      </c>
+      <c r="D95">
+        <v>0.5819149412703553</v>
+      </c>
+      <c r="E95">
+        <v>2.072917634379345</v>
+      </c>
+      <c r="F95">
+        <v>1.759066021800495</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>27</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96">
+        <v>0.75</v>
+      </c>
+      <c r="D96">
+        <v>0.5746313474399183</v>
+      </c>
+      <c r="E96">
+        <v>2.090896151400203</v>
+      </c>
+      <c r="F96">
+        <v>1.773461180503131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>27</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97">
+        <v>0.82</v>
+      </c>
+      <c r="D97">
+        <v>0.5734085504227759</v>
+      </c>
+      <c r="E97">
+        <v>2.09389931906096</v>
+      </c>
+      <c r="F97">
+        <v>1.820962333534598</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98">
+        <v>0.77</v>
+      </c>
+      <c r="D98">
+        <v>0.5649240120357408</v>
+      </c>
+      <c r="E98">
+        <v>2.114619730107293</v>
+      </c>
+      <c r="F98">
+        <v>1.782313192608169</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>30</v>
+      </c>
+      <c r="C99">
+        <v>0.75</v>
+      </c>
+      <c r="D99">
+        <v>0.5644873141215732</v>
+      </c>
+      <c r="E99">
+        <v>2.115680715365056</v>
+      </c>
+      <c r="F99">
+        <v>1.785802808983412</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>27</v>
+      </c>
+      <c r="B100" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100">
+        <v>0.77</v>
+      </c>
+      <c r="D100">
+        <v>0.5611052665623186</v>
+      </c>
+      <c r="E100">
+        <v>2.123879667108334</v>
+      </c>
+      <c r="F100">
+        <v>1.844034314458686</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101">
+        <v>0.7</v>
+      </c>
+      <c r="D101">
+        <v>0.5537816059935983</v>
+      </c>
+      <c r="E101">
+        <v>2.141526519709261</v>
+      </c>
+      <c r="F101">
+        <v>1.819229432473925</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>29</v>
+      </c>
+      <c r="B102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102">
+        <v>1.1</v>
+      </c>
+      <c r="D102">
+        <v>0.5495859774757704</v>
+      </c>
+      <c r="E102">
+        <v>2.151570959594594</v>
+      </c>
+      <c r="F102">
+        <v>1.726609234877269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>29</v>
+      </c>
+      <c r="B103" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103">
+        <v>0.95</v>
+      </c>
+      <c r="D103">
+        <v>0.5478688365624277</v>
+      </c>
+      <c r="E103">
+        <v>2.1556683408861</v>
+      </c>
+      <c r="F103">
+        <v>1.726379188290394</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104">
+        <v>0.7</v>
+      </c>
+      <c r="D104">
+        <v>0.5452059418782369</v>
+      </c>
+      <c r="E104">
+        <v>2.162007088257744</v>
+      </c>
+      <c r="F104">
+        <v>1.873098690072233</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105">
+        <v>1.05</v>
+      </c>
+      <c r="D105">
+        <v>0.5371407856621923</v>
+      </c>
+      <c r="E105">
+        <v>2.181092977228281</v>
+      </c>
+      <c r="F105">
+        <v>1.899438712582113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106">
+        <v>0.7</v>
+      </c>
+      <c r="D106">
+        <v>0.5296229518439262</v>
+      </c>
+      <c r="E106">
+        <v>2.198734463300228</v>
+      </c>
+      <c r="F106">
+        <v>1.778187604415957</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>29</v>
+      </c>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>0.75</v>
+      </c>
+      <c r="D107">
+        <v>0.5288114718554336</v>
+      </c>
+      <c r="E107">
+        <v>2.200630240488766</v>
+      </c>
+      <c r="F107">
+        <v>1.783075659202942</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>29</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>0.77</v>
+      </c>
+      <c r="D108">
+        <v>0.5284696900434036</v>
+      </c>
+      <c r="E108">
+        <v>2.201428221555046</v>
+      </c>
+      <c r="F108">
+        <v>1.784903259463859</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>29</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109">
+        <v>0.8</v>
+      </c>
+      <c r="D109">
+        <v>0.5279057404064762</v>
+      </c>
+      <c r="E109">
+        <v>2.202744280815056</v>
+      </c>
+      <c r="F109">
+        <v>1.787716229156215</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>29</v>
+      </c>
+      <c r="B110" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110">
+        <v>0.82</v>
+      </c>
+      <c r="D110">
+        <v>0.5275055980117935</v>
+      </c>
+      <c r="E110">
+        <v>2.203677595151891</v>
+      </c>
+      <c r="F110">
+        <v>1.789577718365327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>29</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111">
+        <v>0.85</v>
+      </c>
+      <c r="D111">
+        <v>0.5268532049051762</v>
+      </c>
+      <c r="E111">
+        <v>2.205198426031126</v>
+      </c>
+      <c r="F111">
+        <v>1.79234756411123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>29</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112">
+        <v>0.88</v>
+      </c>
+      <c r="D112">
+        <v>0.5261344668575456</v>
+      </c>
+      <c r="E112">
+        <v>2.206872704048495</v>
+      </c>
+      <c r="F112">
+        <v>1.795036501478013</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>29</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113">
+        <v>0.9</v>
+      </c>
+      <c r="D113">
+        <v>0.5255759613035547</v>
+      </c>
+      <c r="E113">
+        <v>2.208172848935418</v>
+      </c>
+      <c r="F113">
+        <v>1.796936738973704</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>29</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114">
+        <v>0.95</v>
+      </c>
+      <c r="D114">
+        <v>0.5242152459718039</v>
+      </c>
+      <c r="E114">
+        <v>2.211337257794889</v>
+      </c>
+      <c r="F114">
+        <v>1.801401038476263</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>29</v>
+      </c>
+      <c r="B115" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>0.5226656770569778</v>
+      </c>
+      <c r="E115">
+        <v>2.214935349123785</v>
+      </c>
+      <c r="F115">
+        <v>1.805693648663204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>29</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116">
+        <v>1.05</v>
+      </c>
+      <c r="D116">
+        <v>0.5210408520484212</v>
+      </c>
+      <c r="E116">
+        <v>2.218701917718316</v>
+      </c>
+      <c r="F116">
+        <v>1.81001363482256</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117">
+        <v>1.1</v>
+      </c>
+      <c r="D117">
+        <v>0.519315554861959</v>
+      </c>
+      <c r="E117">
+        <v>2.222694407654854</v>
+      </c>
+      <c r="F117">
+        <v>1.816436879553126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>27</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118">
+        <v>0.9</v>
+      </c>
+      <c r="D118">
+        <v>0.4984113891545673</v>
+      </c>
+      <c r="E118">
+        <v>2.270510715509737</v>
+      </c>
+      <c r="F118">
+        <v>1.851937659115944</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119">
+        <v>1.05</v>
+      </c>
+      <c r="D119">
+        <v>0.4939439414295869</v>
+      </c>
+      <c r="E119">
+        <v>2.280599563191656</v>
+      </c>
+      <c r="F119">
+        <v>1.946229858510736</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120">
+        <v>0.75</v>
+      </c>
+      <c r="D120">
+        <v>0.4924239821938796</v>
+      </c>
+      <c r="E120">
+        <v>2.284021930468024</v>
+      </c>
+      <c r="F120">
+        <v>1.871429043254157</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>27</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121">
+        <v>0.88</v>
+      </c>
+      <c r="D121">
+        <v>0.490794663230658</v>
+      </c>
+      <c r="E121">
+        <v>2.287684848408686</v>
+      </c>
+      <c r="F121">
+        <v>1.843810996843931</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>27</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122">
+        <v>0.95</v>
+      </c>
+      <c r="D122">
+        <v>0.4850122389918948</v>
+      </c>
+      <c r="E122">
+        <v>2.300637404571513</v>
+      </c>
+      <c r="F122">
+        <v>1.841501790044746</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>27</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123">
+        <v>0.7</v>
+      </c>
+      <c r="D123">
+        <v>0.4799157347846336</v>
+      </c>
+      <c r="E123">
+        <v>2.311993345953505</v>
+      </c>
+      <c r="F123">
+        <v>1.87758606263614</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>29</v>
+      </c>
+      <c r="B124" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124">
+        <v>1.05</v>
+      </c>
+      <c r="D124">
+        <v>0.4762140991921872</v>
+      </c>
+      <c r="E124">
+        <v>2.320206421675429</v>
+      </c>
+      <c r="F124">
+        <v>1.851434845054509</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>29</v>
+      </c>
+      <c r="B125" t="s">
+        <v>30</v>
+      </c>
+      <c r="C125">
+        <v>0.9</v>
+      </c>
+      <c r="D125">
+        <v>0.4758399166491036</v>
+      </c>
+      <c r="E125">
+        <v>2.321035029070614</v>
+      </c>
+      <c r="F125">
+        <v>1.847388216384474</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>29</v>
+      </c>
+      <c r="B126" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126">
+        <v>0.88</v>
+      </c>
+      <c r="D126">
+        <v>0.4752960368206736</v>
+      </c>
+      <c r="E126">
+        <v>2.322238894911589</v>
+      </c>
+      <c r="F126">
+        <v>1.848496666832078</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>13</v>
+      </c>
+      <c r="B127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127">
+        <v>0.85</v>
+      </c>
+      <c r="D127">
+        <v>0.4716130707059426</v>
+      </c>
+      <c r="E127">
+        <v>2.330374693402263</v>
+      </c>
+      <c r="F127">
+        <v>2.026118577083474</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128">
+        <v>0.85</v>
+      </c>
+      <c r="D128">
+        <v>0.4708996090244463</v>
+      </c>
+      <c r="E128">
+        <v>2.331947472823428</v>
+      </c>
+      <c r="F128">
+        <v>1.862840051631438</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129">
+        <v>0.85</v>
+      </c>
+      <c r="D129">
+        <v>0.4684057810550275</v>
+      </c>
+      <c r="E129">
+        <v>2.337436638451357</v>
+      </c>
+      <c r="F129">
+        <v>2.021017583054427</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130">
+        <v>0.95</v>
+      </c>
+      <c r="D130">
+        <v>0.4613900622049008</v>
+      </c>
+      <c r="E130">
+        <v>2.352810250502384</v>
+      </c>
+      <c r="F130">
+        <v>1.978392073284462</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>27</v>
+      </c>
+      <c r="B131" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131">
+        <v>0.75</v>
+      </c>
+      <c r="D131">
+        <v>0.4602543727970713</v>
+      </c>
+      <c r="E131">
+        <v>2.355289460806179</v>
+      </c>
+      <c r="F131">
+        <v>1.945875912657227</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132">
+        <v>0.85</v>
+      </c>
+      <c r="D132">
+        <v>0.4475337859088663</v>
+      </c>
+      <c r="E132">
+        <v>2.382882262335068</v>
+      </c>
+      <c r="F132">
+        <v>1.913471658055409</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>26</v>
+      </c>
+      <c r="B133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133">
+        <v>0.001</v>
+      </c>
+      <c r="D133">
+        <v>0.4391651842205969</v>
+      </c>
+      <c r="E133">
+        <v>2.400862042790428</v>
+      </c>
+      <c r="F133">
+        <v>2.003542156276868</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>13</v>
+      </c>
+      <c r="B134" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134">
+        <v>0.75</v>
+      </c>
+      <c r="D134">
+        <v>0.4359412463513603</v>
+      </c>
+      <c r="E134">
+        <v>2.407752786814408</v>
+      </c>
+      <c r="F134">
+        <v>2.063932842686188</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135">
+        <v>0.4338479966398204</v>
+      </c>
+      <c r="E135">
+        <v>2.412216293942442</v>
+      </c>
+      <c r="F135">
+        <v>2.018247520737008</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136">
+        <v>0.77</v>
+      </c>
+      <c r="D136">
+        <v>0.4274831508235948</v>
+      </c>
+      <c r="E136">
+        <v>2.425737816219541</v>
+      </c>
+      <c r="F136">
+        <v>1.819262571815272</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137">
+        <v>0.77</v>
+      </c>
+      <c r="D137">
+        <v>0.4226875403052212</v>
+      </c>
+      <c r="E137">
+        <v>2.435876063639077</v>
+      </c>
+      <c r="F137">
+        <v>2.018781619952099</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" t="s">
+        <v>30</v>
+      </c>
+      <c r="C138">
+        <v>1.1</v>
+      </c>
+      <c r="D138">
+        <v>0.4172699868737533</v>
+      </c>
+      <c r="E138">
+        <v>2.447278618403665</v>
+      </c>
+      <c r="F138">
+        <v>2.094640718900416</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>13</v>
+      </c>
+      <c r="B139" t="s">
+        <v>30</v>
+      </c>
+      <c r="C139">
+        <v>1.1</v>
+      </c>
+      <c r="D139">
+        <v>0.4169212077206265</v>
+      </c>
+      <c r="E139">
+        <v>2.448010888977957</v>
+      </c>
+      <c r="F139">
+        <v>1.889550379569658</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
+        <v>30</v>
+      </c>
+      <c r="C140">
+        <v>0.7</v>
+      </c>
+      <c r="D140">
+        <v>0.4166605505302128</v>
+      </c>
+      <c r="E140">
+        <v>2.448558002294655</v>
+      </c>
+      <c r="F140">
+        <v>2.061235758505888</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>27</v>
+      </c>
+      <c r="B141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141">
+        <v>0.8</v>
+      </c>
+      <c r="D141">
+        <v>0.4164114435641191</v>
+      </c>
+      <c r="E141">
+        <v>2.449080757743261</v>
+      </c>
+      <c r="F141">
+        <v>1.923174574165032</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>24</v>
+      </c>
+      <c r="B142" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142">
+        <v>0.77</v>
+      </c>
+      <c r="D142">
+        <v>0.4155592516854248</v>
+      </c>
+      <c r="E142">
+        <v>2.450868254552204</v>
+      </c>
+      <c r="F142">
+        <v>2.12854029541344</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>23</v>
+      </c>
+      <c r="B143" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143">
+        <v>0.75</v>
+      </c>
+      <c r="D143">
+        <v>0.4033351763532053</v>
+      </c>
+      <c r="E143">
+        <v>2.476366611610083</v>
+      </c>
+      <c r="F143">
+        <v>2.053445506602018</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>23</v>
+      </c>
+      <c r="B144" t="s">
+        <v>30</v>
+      </c>
+      <c r="C144">
+        <v>0.77</v>
+      </c>
+      <c r="D144">
+        <v>0.4006649457548361</v>
+      </c>
+      <c r="E144">
+        <v>2.481901618882083</v>
+      </c>
+      <c r="F144">
+        <v>2.207560072806948</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>23</v>
+      </c>
+      <c r="B145" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145">
+        <v>0.9</v>
+      </c>
+      <c r="D145">
+        <v>0.4001621716922621</v>
+      </c>
+      <c r="E145">
+        <v>2.482942417482613</v>
+      </c>
+      <c r="F145">
+        <v>2.130683485156428</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>30</v>
+      </c>
+      <c r="C146">
+        <v>0.75</v>
+      </c>
+      <c r="D146">
+        <v>0.3994066925922232</v>
+      </c>
+      <c r="E146">
+        <v>2.484505524003371</v>
+      </c>
+      <c r="F146">
+        <v>2.110523785139239</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>27</v>
+      </c>
+      <c r="B147" t="s">
+        <v>30</v>
+      </c>
+      <c r="C147">
+        <v>1.05</v>
+      </c>
+      <c r="D147">
+        <v>0.398421768409855</v>
+      </c>
+      <c r="E147">
+        <v>2.486541882986104</v>
+      </c>
+      <c r="F147">
+        <v>1.930479435151927</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>23</v>
+      </c>
+      <c r="B148" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148">
+        <v>0.88</v>
+      </c>
+      <c r="D148">
+        <v>0.3944336604704659</v>
+      </c>
+      <c r="E148">
+        <v>2.494770419080432</v>
+      </c>
+      <c r="F148">
+        <v>2.097351236437786</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>27</v>
+      </c>
+      <c r="B149" t="s">
+        <v>30</v>
+      </c>
+      <c r="C149">
+        <v>1.1</v>
+      </c>
+      <c r="D149">
+        <v>0.3934096840371295</v>
+      </c>
+      <c r="E149">
+        <v>2.496878781903838</v>
+      </c>
+      <c r="F149">
+        <v>1.989078870185322</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>28</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150">
+        <v>0.8</v>
+      </c>
+      <c r="D150">
+        <v>0.3874212447903055</v>
+      </c>
+      <c r="E150">
+        <v>2.509173475618787</v>
+      </c>
+      <c r="F150">
+        <v>2.144524550013596</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>24</v>
+      </c>
+      <c r="B151" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151">
+        <v>0.82</v>
+      </c>
+      <c r="D151">
+        <v>0.3872473286143814</v>
+      </c>
+      <c r="E151">
+        <v>2.509529637894173</v>
+      </c>
+      <c r="F151">
+        <v>2.163593528504058</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>27</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>0.3800035328629411</v>
+      </c>
+      <c r="E152">
+        <v>2.524319544841323</v>
+      </c>
+      <c r="F152">
+        <v>2.046484152049544</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>23</v>
+      </c>
+      <c r="B153" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153">
+        <v>0.0001</v>
+      </c>
+      <c r="D153">
+        <v>0.3796255293680878</v>
+      </c>
+      <c r="E153">
+        <v>2.525088949397639</v>
+      </c>
+      <c r="F153">
+        <v>2.076173692917623</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>27</v>
+      </c>
+      <c r="B154" t="s">
+        <v>30</v>
+      </c>
+      <c r="C154">
+        <v>0.82</v>
+      </c>
+      <c r="D154">
+        <v>0.3794356992071144</v>
+      </c>
+      <c r="E154">
+        <v>2.525475249448277</v>
+      </c>
+      <c r="F154">
+        <v>2.001041199232691</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>26</v>
+      </c>
+      <c r="B155" t="s">
+        <v>30</v>
+      </c>
+      <c r="C155">
+        <v>1.05</v>
+      </c>
+      <c r="D155">
+        <v>0.3732306412724217</v>
+      </c>
+      <c r="E155">
+        <v>2.53807002950585</v>
+      </c>
+      <c r="F155">
+        <v>2.023711002300701</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156" t="s">
+        <v>30</v>
+      </c>
+      <c r="C156">
+        <v>0.7</v>
+      </c>
+      <c r="D156">
+        <v>0.369991851221633</v>
+      </c>
+      <c r="E156">
+        <v>2.544619235971457</v>
+      </c>
+      <c r="F156">
+        <v>2.12833262264798</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="B157" t="s">
+        <v>30</v>
+      </c>
+      <c r="C157">
+        <v>0.001</v>
+      </c>
+      <c r="D157">
+        <v>0.3688388461652192</v>
+      </c>
+      <c r="E157">
+        <v>2.54694668021743</v>
+      </c>
+      <c r="F157">
+        <v>2.023646784516287</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>16</v>
+      </c>
+      <c r="B158" t="s">
+        <v>30</v>
+      </c>
+      <c r="C158">
+        <v>0.88</v>
+      </c>
+      <c r="D158">
+        <v>0.3602752731244746</v>
+      </c>
+      <c r="E158">
+        <v>2.564166909054055</v>
+      </c>
+      <c r="F158">
+        <v>2.179333082194349</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>26</v>
+      </c>
+      <c r="B159" t="s">
+        <v>30</v>
+      </c>
+      <c r="C159">
+        <v>0.88</v>
+      </c>
+      <c r="D159">
+        <v>0.3493612123240908</v>
+      </c>
+      <c r="E159">
+        <v>2.585947463947719</v>
+      </c>
+      <c r="F159">
+        <v>2.179400144802139</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>26</v>
+      </c>
+      <c r="B160" t="s">
+        <v>30</v>
+      </c>
+      <c r="C160">
+        <v>0.77</v>
+      </c>
+      <c r="D160">
+        <v>0.3491243631056199</v>
+      </c>
+      <c r="E160">
+        <v>2.586418096745831</v>
+      </c>
+      <c r="F160">
+        <v>2.074797791523686</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>23</v>
+      </c>
+      <c r="B161" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161">
+        <v>0.7</v>
+      </c>
+      <c r="D161">
+        <v>0.3481137053289933</v>
+      </c>
+      <c r="E161">
+        <v>2.588425369314971</v>
+      </c>
+      <c r="F161">
+        <v>2.256943309885917</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>23</v>
+      </c>
+      <c r="B162" t="s">
+        <v>30</v>
+      </c>
+      <c r="C162">
+        <v>1.1</v>
+      </c>
+      <c r="D162">
+        <v>0.3410878926395429</v>
+      </c>
+      <c r="E162">
+        <v>2.602336579095428</v>
+      </c>
+      <c r="F162">
+        <v>2.194832063969626</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>26</v>
+      </c>
+      <c r="B163" t="s">
+        <v>30</v>
+      </c>
+      <c r="C163">
+        <v>1.1</v>
+      </c>
+      <c r="D163">
+        <v>0.3408811573142738</v>
+      </c>
+      <c r="E163">
+        <v>2.602744791890759</v>
+      </c>
+      <c r="F163">
+        <v>2.056830501453611</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>16</v>
+      </c>
+      <c r="B164" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164">
+        <v>1.1</v>
+      </c>
+      <c r="D164">
+        <v>0.3393091328588719</v>
+      </c>
+      <c r="E164">
+        <v>2.605846767938296</v>
+      </c>
+      <c r="F164">
+        <v>2.251457072323063</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C165">
+        <v>0.85</v>
+      </c>
+      <c r="D165">
+        <v>0.3376271108923768</v>
+      </c>
+      <c r="E165">
+        <v>2.609161711122287</v>
+      </c>
+      <c r="F165">
+        <v>2.198000556987231</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>0.3362748636474319</v>
+      </c>
+      <c r="E166">
+        <v>2.611823680604038</v>
+      </c>
+      <c r="F166">
+        <v>2.152145468100312</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>28</v>
+      </c>
+      <c r="B167" t="s">
+        <v>30</v>
+      </c>
+      <c r="C167">
+        <v>0.95</v>
+      </c>
+      <c r="D167">
+        <v>0.3343533415315767</v>
+      </c>
+      <c r="E167">
+        <v>2.615601637471831</v>
+      </c>
+      <c r="F167">
+        <v>2.252860084316811</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>16</v>
+      </c>
+      <c r="B168" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168">
+        <v>0.8</v>
+      </c>
+      <c r="D168">
+        <v>0.3319534074222521</v>
+      </c>
+      <c r="E168">
+        <v>2.620312563033513</v>
+      </c>
+      <c r="F168">
+        <v>2.149039202109434</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>16</v>
+      </c>
+      <c r="B169" t="s">
+        <v>30</v>
+      </c>
+      <c r="C169">
+        <v>1.05</v>
+      </c>
+      <c r="D169">
+        <v>0.3221018418695969</v>
+      </c>
+      <c r="E169">
+        <v>2.639562498063191</v>
+      </c>
+      <c r="F169">
+        <v>2.243528481323304</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" t="s">
+        <v>30</v>
+      </c>
+      <c r="C170">
+        <v>0.95</v>
+      </c>
+      <c r="D170">
+        <v>0.3212442577997112</v>
+      </c>
+      <c r="E170">
+        <v>2.641231577157926</v>
+      </c>
+      <c r="F170">
+        <v>2.212811483117298</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>29</v>
+      </c>
+      <c r="B171" t="s">
+        <v>30</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171">
+        <v>0.3167621484617317</v>
+      </c>
+      <c r="E171">
+        <v>2.649937808975666</v>
+      </c>
+      <c r="F171">
+        <v>2.080886389590011</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>26</v>
+      </c>
+      <c r="B172" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172">
+        <v>0.75</v>
+      </c>
+      <c r="D172">
+        <v>0.3146386512347004</v>
+      </c>
+      <c r="E172">
+        <v>2.654052605957318</v>
+      </c>
+      <c r="F172">
+        <v>2.143506835035043</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>16</v>
+      </c>
+      <c r="B173" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173">
+        <v>0.82</v>
+      </c>
+      <c r="D173">
+        <v>0.3115561004227301</v>
+      </c>
+      <c r="E173">
+        <v>2.66001447807952</v>
+      </c>
+      <c r="F173">
+        <v>2.165376567219889</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>26</v>
+      </c>
+      <c r="B174" t="s">
+        <v>30</v>
+      </c>
+      <c r="C174">
+        <v>0.7</v>
+      </c>
+      <c r="D174">
+        <v>0.311255939815998</v>
+      </c>
+      <c r="E174">
+        <v>2.660594296239246</v>
+      </c>
+      <c r="F174">
+        <v>2.158001911683042</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>13</v>
+      </c>
+      <c r="B175" t="s">
+        <v>30</v>
+      </c>
+      <c r="C175">
+        <v>0.77</v>
+      </c>
+      <c r="D175">
+        <v>0.3107212218071125</v>
+      </c>
+      <c r="E175">
+        <v>2.661626894373966</v>
+      </c>
+      <c r="F175">
+        <v>2.280744848037661</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>13</v>
+      </c>
+      <c r="B176" t="s">
+        <v>30</v>
+      </c>
+      <c r="C176">
+        <v>0.82</v>
+      </c>
+      <c r="D176">
+        <v>0.3090569694423525</v>
+      </c>
+      <c r="E176">
+        <v>2.664838184497489</v>
+      </c>
+      <c r="F176">
+        <v>2.280744595988887</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>16</v>
+      </c>
+      <c r="B177" t="s">
+        <v>30</v>
+      </c>
+      <c r="C177">
+        <v>0.95</v>
+      </c>
+      <c r="D177">
+        <v>0.3056459965911978</v>
+      </c>
+      <c r="E177">
+        <v>2.671407828920646</v>
+      </c>
+      <c r="F177">
+        <v>2.193567868268761</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>25</v>
+      </c>
+      <c r="B178" t="s">
+        <v>30</v>
+      </c>
+      <c r="C178">
+        <v>0.7</v>
+      </c>
+      <c r="D178">
+        <v>0.3052824003066541</v>
+      </c>
+      <c r="E178">
+        <v>2.672107174523348</v>
+      </c>
+      <c r="F178">
+        <v>2.203498700346851</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>16</v>
+      </c>
+      <c r="B179" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179">
+        <v>0.85</v>
+      </c>
+      <c r="D179">
+        <v>0.3046835036662603</v>
+      </c>
+      <c r="E179">
+        <v>2.673258700885966</v>
+      </c>
+      <c r="F179">
+        <v>2.236437626072947</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>25</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180">
+        <v>0.001</v>
+      </c>
+      <c r="D180">
+        <v>0.3039511889281812</v>
+      </c>
+      <c r="E180">
+        <v>2.674666082681218</v>
+      </c>
+      <c r="F180">
+        <v>2.22287909561886</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>29</v>
+      </c>
+      <c r="B181" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181">
+        <v>0.001</v>
+      </c>
+      <c r="D181">
+        <v>0.3010712239350386</v>
+      </c>
+      <c r="E181">
+        <v>2.680193707394972</v>
+      </c>
+      <c r="F181">
+        <v>2.077605539753887</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>24</v>
+      </c>
+      <c r="B182" t="s">
+        <v>30</v>
+      </c>
+      <c r="C182">
+        <v>1.1</v>
+      </c>
+      <c r="D182">
+        <v>0.300724946237816</v>
+      </c>
+      <c r="E182">
+        <v>2.680857563578766</v>
+      </c>
+      <c r="F182">
+        <v>2.216853539474539</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>25</v>
+      </c>
+      <c r="B183" t="s">
+        <v>30</v>
+      </c>
+      <c r="C183">
+        <v>0.82</v>
+      </c>
+      <c r="D183">
+        <v>0.2987958562436414</v>
+      </c>
+      <c r="E183">
+        <v>2.684552857477403</v>
+      </c>
+      <c r="F183">
+        <v>2.223040508108689</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>16</v>
+      </c>
+      <c r="B184" t="s">
+        <v>30</v>
+      </c>
+      <c r="C184">
+        <v>0.9</v>
+      </c>
+      <c r="D184">
+        <v>0.2954551350410562</v>
+      </c>
+      <c r="E184">
+        <v>2.690940217145618</v>
+      </c>
+      <c r="F184">
+        <v>2.248641016345622</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>26</v>
+      </c>
+      <c r="B185" t="s">
+        <v>30</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185">
+        <v>0.2917096628276981</v>
+      </c>
+      <c r="E185">
+        <v>2.69808346849769</v>
+      </c>
+      <c r="F185">
+        <v>2.083290572013006</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>16</v>
+      </c>
+      <c r="B186" t="s">
+        <v>30</v>
+      </c>
+      <c r="C186">
+        <v>0.77</v>
+      </c>
+      <c r="D186">
+        <v>0.2883027317058857</v>
+      </c>
+      <c r="E186">
+        <v>2.704564678802479</v>
+      </c>
+      <c r="F186">
+        <v>2.302777080725334</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>28</v>
+      </c>
+      <c r="B187" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187">
+        <v>1.05</v>
+      </c>
+      <c r="D187">
+        <v>0.2861485049363149</v>
+      </c>
+      <c r="E187">
+        <v>2.708654791062652</v>
+      </c>
+      <c r="F187">
+        <v>2.318144186730458</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>16</v>
+      </c>
+      <c r="B188" t="s">
+        <v>30</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>0.2855375959985648</v>
+      </c>
+      <c r="E188">
+        <v>2.709813566770945</v>
+      </c>
+      <c r="F188">
+        <v>2.259667395467532</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>25</v>
+      </c>
+      <c r="B189" t="s">
+        <v>30</v>
+      </c>
+      <c r="C189">
+        <v>0.95</v>
+      </c>
+      <c r="D189">
+        <v>0.2827008295492188</v>
+      </c>
+      <c r="E189">
+        <v>2.715187882396009</v>
+      </c>
+      <c r="F189">
+        <v>2.1958250439864</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>25</v>
+      </c>
+      <c r="B190" t="s">
+        <v>30</v>
+      </c>
+      <c r="C190">
+        <v>0.9</v>
+      </c>
+      <c r="D190">
+        <v>0.2798628172932626</v>
+      </c>
+      <c r="E190">
+        <v>2.720553934568179</v>
+      </c>
+      <c r="F190">
+        <v>2.247196480673123</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>28</v>
+      </c>
+      <c r="B191" t="s">
+        <v>30</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191">
+        <v>0.2775274732718105</v>
+      </c>
+      <c r="E191">
+        <v>2.724961627258579</v>
+      </c>
+      <c r="F191">
+        <v>2.26574805885515</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>26</v>
+      </c>
+      <c r="B192" t="s">
+        <v>30</v>
+      </c>
+      <c r="C192">
+        <v>0.95</v>
+      </c>
+      <c r="D192">
+        <v>0.2772499035844364</v>
+      </c>
+      <c r="E192">
+        <v>2.725485034090704</v>
+      </c>
+      <c r="F192">
+        <v>2.250285856949144</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>13</v>
+      </c>
+      <c r="B193" t="s">
+        <v>30</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193">
+        <v>0.2718084281648739</v>
+      </c>
+      <c r="E193">
+        <v>2.735725676075997</v>
+      </c>
+      <c r="F193">
+        <v>2.365372210318407</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>26</v>
+      </c>
+      <c r="B194" t="s">
+        <v>30</v>
+      </c>
+      <c r="C194">
+        <v>0.9</v>
+      </c>
+      <c r="D194">
+        <v>0.2692389499802845</v>
+      </c>
+      <c r="E194">
+        <v>2.740548031691084</v>
+      </c>
+      <c r="F194">
+        <v>2.259221712549883</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>29</v>
+      </c>
+      <c r="B195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C195">
+        <v>0.0001</v>
+      </c>
+      <c r="D195">
+        <v>0.2644973747150219</v>
+      </c>
+      <c r="E195">
+        <v>2.749424739062891</v>
+      </c>
+      <c r="F195">
+        <v>2.271096209073141</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>24</v>
+      </c>
+      <c r="B196" t="s">
+        <v>30</v>
+      </c>
+      <c r="C196">
+        <v>0.001</v>
+      </c>
+      <c r="D196">
+        <v>0.2631305376047324</v>
+      </c>
+      <c r="E196">
+        <v>2.751978279532533</v>
+      </c>
+      <c r="F196">
+        <v>2.137725564781212</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>13</v>
+      </c>
+      <c r="B197" t="s">
+        <v>30</v>
+      </c>
+      <c r="C197">
+        <v>0.9</v>
+      </c>
+      <c r="D197">
+        <v>0.2622444399633257</v>
+      </c>
+      <c r="E197">
+        <v>2.753632431955054</v>
+      </c>
+      <c r="F197">
+        <v>2.275363644829032</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>26</v>
+      </c>
+      <c r="B198" t="s">
+        <v>30</v>
+      </c>
+      <c r="C198">
+        <v>0.8</v>
+      </c>
+      <c r="D198">
+        <v>0.2570478522790097</v>
+      </c>
+      <c r="E198">
+        <v>2.763313404410696</v>
+      </c>
+      <c r="F198">
+        <v>2.318405568512563</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>26</v>
+      </c>
+      <c r="B199" t="s">
+        <v>30</v>
+      </c>
+      <c r="C199">
+        <v>0.82</v>
+      </c>
+      <c r="D199">
+        <v>0.2556052569828794</v>
+      </c>
+      <c r="E199">
+        <v>2.765994875707463</v>
+      </c>
+      <c r="F199">
+        <v>2.239317221519004</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>23</v>
+      </c>
+      <c r="B200" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200">
+        <v>0.82</v>
+      </c>
+      <c r="D200">
+        <v>0.2421043728527156</v>
+      </c>
+      <c r="E200">
+        <v>2.790965211204348</v>
+      </c>
+      <c r="F200">
+        <v>2.283361221910785</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>23</v>
+      </c>
+      <c r="B201" t="s">
+        <v>30</v>
+      </c>
+      <c r="C201">
+        <v>0.8</v>
+      </c>
+      <c r="D201">
+        <v>0.2395427377927639</v>
+      </c>
+      <c r="E201">
+        <v>2.795677867617097</v>
+      </c>
+      <c r="F201">
+        <v>2.392505766759973</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>24</v>
+      </c>
+      <c r="B202" t="s">
+        <v>30</v>
+      </c>
+      <c r="C202">
+        <v>0.75</v>
+      </c>
+      <c r="D202">
+        <v>0.2346845326915796</v>
+      </c>
+      <c r="E202">
+        <v>2.804593788304627</v>
+      </c>
+      <c r="F202">
+        <v>2.193711076149026</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>25</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203">
+        <v>0.0001</v>
+      </c>
+      <c r="D203">
+        <v>0.2318982287480243</v>
+      </c>
+      <c r="E203">
+        <v>2.809694528728313</v>
+      </c>
+      <c r="F203">
+        <v>2.438914460774928</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>13</v>
+      </c>
+      <c r="B204" t="s">
+        <v>30</v>
+      </c>
+      <c r="C204">
+        <v>0.7</v>
+      </c>
+      <c r="D204">
+        <v>0.2297559550591222</v>
+      </c>
+      <c r="E204">
+        <v>2.813609988771889</v>
+      </c>
+      <c r="F204">
+        <v>2.320071235826781</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>24</v>
+      </c>
+      <c r="B205" t="s">
+        <v>30</v>
+      </c>
+      <c r="C205">
+        <v>0.85</v>
+      </c>
+      <c r="D205">
+        <v>0.2225796907691604</v>
+      </c>
+      <c r="E205">
+        <v>2.826686621507108</v>
+      </c>
+      <c r="F205">
+        <v>2.432076738396043</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>24</v>
+      </c>
+      <c r="B206" t="s">
+        <v>30</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206">
+        <v>0.2212878350509117</v>
+      </c>
+      <c r="E206">
+        <v>2.829034229021785</v>
+      </c>
+      <c r="F206">
+        <v>2.371354984822718</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>27</v>
+      </c>
+      <c r="B207" t="s">
+        <v>30</v>
+      </c>
+      <c r="C207">
+        <v>0.001</v>
+      </c>
+      <c r="D207">
+        <v>0.2156274825302578</v>
+      </c>
+      <c r="E207">
+        <v>2.8392975441154</v>
+      </c>
+      <c r="F207">
+        <v>2.277112403906289</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>16</v>
+      </c>
+      <c r="B208" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208">
+        <v>0.7</v>
+      </c>
+      <c r="D208">
+        <v>0.2137479362662523</v>
+      </c>
+      <c r="E208">
+        <v>2.842697330477431</v>
+      </c>
+      <c r="F208">
+        <v>2.377811128828703</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>24</v>
+      </c>
+      <c r="B209" t="s">
+        <v>30</v>
+      </c>
+      <c r="C209">
+        <v>0.9</v>
+      </c>
+      <c r="D209">
+        <v>0.2130838736716167</v>
+      </c>
+      <c r="E209">
+        <v>2.843897537529277</v>
+      </c>
+      <c r="F209">
+        <v>2.404534084902068</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>28</v>
+      </c>
+      <c r="B210" t="s">
+        <v>30</v>
+      </c>
+      <c r="C210">
+        <v>0.9</v>
+      </c>
+      <c r="D210">
+        <v>0.2048519591401737</v>
+      </c>
+      <c r="E210">
+        <v>2.85873381681224</v>
+      </c>
+      <c r="F210">
+        <v>2.433092557309335</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>25</v>
+      </c>
+      <c r="B211" t="s">
+        <v>30</v>
+      </c>
+      <c r="C211">
+        <v>1.05</v>
+      </c>
+      <c r="D211">
+        <v>0.203987890308595</v>
+      </c>
+      <c r="E211">
+        <v>2.860286654752295</v>
+      </c>
+      <c r="F211">
+        <v>2.352211502562753</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>26</v>
+      </c>
+      <c r="B212" t="s">
+        <v>30</v>
+      </c>
+      <c r="C212">
+        <v>0.85</v>
+      </c>
+      <c r="D212">
+        <v>0.1907143611784766</v>
+      </c>
+      <c r="E212">
+        <v>2.884035748687475</v>
+      </c>
+      <c r="F212">
+        <v>2.417200129138402</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>16</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213">
+        <v>0.001</v>
+      </c>
+      <c r="D213">
+        <v>0.1903193417648189</v>
+      </c>
+      <c r="E213">
+        <v>2.884739524381864</v>
+      </c>
+      <c r="F213">
+        <v>2.419547850084943</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>25</v>
+      </c>
+      <c r="B214" t="s">
+        <v>30</v>
+      </c>
+      <c r="C214">
+        <v>0.8</v>
+      </c>
+      <c r="D214">
+        <v>0.1782535793270278</v>
+      </c>
+      <c r="E214">
+        <v>2.906154058524359</v>
+      </c>
+      <c r="F214">
+        <v>2.281180088290495</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>13</v>
+      </c>
+      <c r="B215" t="s">
+        <v>30</v>
+      </c>
+      <c r="C215">
+        <v>0.8</v>
+      </c>
+      <c r="D215">
+        <v>0.1762678157067646</v>
+      </c>
+      <c r="E215">
+        <v>2.909663324081035</v>
+      </c>
+      <c r="F215">
+        <v>2.461016154919597</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>25</v>
+      </c>
+      <c r="B216" t="s">
+        <v>30</v>
+      </c>
+      <c r="C216">
+        <v>0.88</v>
+      </c>
+      <c r="D216">
+        <v>0.17185775266932</v>
+      </c>
+      <c r="E216">
+        <v>2.91744174415195</v>
+      </c>
+      <c r="F216">
+        <v>2.421008011962846</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>28</v>
+      </c>
+      <c r="B217" t="s">
+        <v>30</v>
+      </c>
+      <c r="C217">
+        <v>0.82</v>
+      </c>
+      <c r="D217">
+        <v>0.1460435568136673</v>
+      </c>
+      <c r="E217">
+        <v>2.962562916538078</v>
+      </c>
+      <c r="F217">
+        <v>2.447456801385002</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>25</v>
+      </c>
+      <c r="B218" t="s">
+        <v>30</v>
+      </c>
+      <c r="C218">
+        <v>0.85</v>
+      </c>
+      <c r="D218">
+        <v>0.1448936263355246</v>
+      </c>
+      <c r="E218">
+        <v>2.964556926488826</v>
+      </c>
+      <c r="F218">
+        <v>2.379172472349279</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>24</v>
+      </c>
+      <c r="B219" t="s">
+        <v>30</v>
+      </c>
+      <c r="C219">
+        <v>1.05</v>
+      </c>
+      <c r="D219">
+        <v>0.1423960224422626</v>
+      </c>
+      <c r="E219">
+        <v>2.968883224595749</v>
+      </c>
+      <c r="F219">
+        <v>2.314266401157819</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220" t="s">
+        <v>30</v>
+      </c>
+      <c r="C220">
+        <v>0.88</v>
+      </c>
+      <c r="D220">
+        <v>0.1360541203602753</v>
+      </c>
+      <c r="E220">
+        <v>2.979840313647687</v>
+      </c>
+      <c r="F220">
+        <v>2.399257577389676</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>13</v>
+      </c>
+      <c r="B221" t="s">
+        <v>30</v>
+      </c>
+      <c r="C221">
+        <v>0.95</v>
+      </c>
+      <c r="D221">
+        <v>0.1342397049044468</v>
+      </c>
+      <c r="E221">
+        <v>2.982967727483677</v>
+      </c>
+      <c r="F221">
+        <v>2.56825086350126</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>28</v>
+      </c>
+      <c r="B222" t="s">
+        <v>30</v>
+      </c>
+      <c r="C222">
+        <v>0.88</v>
+      </c>
+      <c r="D222">
+        <v>0.1243939544517406</v>
+      </c>
+      <c r="E222">
+        <v>2.999881489336526</v>
+      </c>
+      <c r="F222">
+        <v>2.451560925711554</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" t="s">
+        <v>30</v>
+      </c>
+      <c r="C223">
+        <v>0.0001</v>
+      </c>
+      <c r="D223">
+        <v>0.1189814624530088</v>
+      </c>
+      <c r="E223">
+        <v>3.009138974597622</v>
+      </c>
+      <c r="F223">
+        <v>2.425218752151223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>25</v>
+      </c>
+      <c r="B224" t="s">
+        <v>30</v>
+      </c>
+      <c r="C224">
+        <v>1.1</v>
+      </c>
+      <c r="D224">
+        <v>0.1064628437907353</v>
+      </c>
+      <c r="E224">
+        <v>3.030442379390363</v>
+      </c>
+      <c r="F224">
+        <v>2.41380155280073</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>13</v>
+      </c>
+      <c r="B225" t="s">
+        <v>30</v>
+      </c>
+      <c r="C225">
+        <v>0.88</v>
+      </c>
+      <c r="D225">
+        <v>0.09684908368721012</v>
+      </c>
+      <c r="E225">
+        <v>3.046701356416072</v>
+      </c>
+      <c r="F225">
+        <v>2.409368299634703</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>24</v>
+      </c>
+      <c r="B226" t="s">
+        <v>30</v>
+      </c>
+      <c r="C226">
+        <v>0.0001</v>
+      </c>
+      <c r="D226">
+        <v>0.09216514320844715</v>
+      </c>
+      <c r="E226">
+        <v>3.054591573209497</v>
+      </c>
+      <c r="F226">
+        <v>2.318456614145817</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>25</v>
+      </c>
+      <c r="B227" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227">
+        <v>0.0001</v>
+      </c>
+      <c r="D227">
+        <v>0.07815665312880016</v>
+      </c>
+      <c r="E227">
+        <v>3.078068534104723</v>
+      </c>
+      <c r="F227">
+        <v>2.63033014468891</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>13</v>
+      </c>
+      <c r="B228" t="s">
+        <v>30</v>
+      </c>
+      <c r="C228">
+        <v>0.001</v>
+      </c>
+      <c r="D228">
+        <v>0.065522779293406</v>
+      </c>
+      <c r="E228">
+        <v>3.099089239546023</v>
+      </c>
+      <c r="F228">
+        <v>2.774314943362893</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>27</v>
+      </c>
+      <c r="B229" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229">
+        <v>0.001</v>
+      </c>
+      <c r="D229">
+        <v>0.06418931447388121</v>
+      </c>
+      <c r="E229">
+        <v>3.101299594807678</v>
+      </c>
+      <c r="F229">
+        <v>2.500840086083931</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" t="s">
+        <v>30</v>
+      </c>
+      <c r="C230">
+        <v>0.75</v>
+      </c>
+      <c r="D230">
+        <v>0.06188555555189934</v>
+      </c>
+      <c r="E230">
+        <v>3.105114605146237</v>
+      </c>
+      <c r="F230">
+        <v>2.494658354870223</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>28</v>
+      </c>
+      <c r="B231" t="s">
+        <v>30</v>
+      </c>
+      <c r="C231">
+        <v>0.77</v>
+      </c>
+      <c r="D231">
+        <v>0.05537398143615968</v>
+      </c>
+      <c r="E231">
+        <v>3.115872471234084</v>
+      </c>
+      <c r="F231">
+        <v>2.4640652230016</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232">
+        <v>0.0001</v>
+      </c>
+      <c r="D232">
+        <v>0.05524045121349097</v>
+      </c>
+      <c r="E232">
+        <v>3.11609268983611</v>
+      </c>
+      <c r="F232">
+        <v>2.630715109100399</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>23</v>
+      </c>
+      <c r="B233" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233">
+        <v>0.001</v>
+      </c>
+      <c r="D233">
+        <v>0.05265966674226974</v>
+      </c>
+      <c r="E233">
+        <v>3.120345877378859</v>
+      </c>
+      <c r="F233">
+        <v>2.420579735534829</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" t="s">
+        <v>30</v>
+      </c>
+      <c r="C234">
+        <v>0.001</v>
+      </c>
+      <c r="D234">
+        <v>0.04872900199447727</v>
+      </c>
+      <c r="E234">
+        <v>3.126812580550763</v>
+      </c>
+      <c r="F234">
+        <v>2.618156171856139</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>23</v>
+      </c>
+      <c r="B235" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235">
+        <v>0.0001</v>
+      </c>
+      <c r="D235">
+        <v>0.04339091069318046</v>
+      </c>
+      <c r="E235">
+        <v>3.135573417741002</v>
+      </c>
+      <c r="F235">
+        <v>2.576652094891734</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236">
+        <v>0.0001</v>
+      </c>
+      <c r="D236">
+        <v>0.04245696144682343</v>
+      </c>
+      <c r="E236">
+        <v>3.137103693815818</v>
+      </c>
+      <c r="F236">
+        <v>2.687200782252483</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>23</v>
+      </c>
+      <c r="B237" t="s">
+        <v>30</v>
+      </c>
+      <c r="C237">
+        <v>0.001</v>
+      </c>
+      <c r="D237">
+        <v>0.007241874857319641</v>
+      </c>
+      <c r="E237">
+        <v>3.194268712063478</v>
+      </c>
+      <c r="F237">
+        <v>2.574362053304049</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>24</v>
+      </c>
+      <c r="B238" t="s">
+        <v>30</v>
+      </c>
+      <c r="C238">
+        <v>0.8</v>
+      </c>
+      <c r="D238">
+        <v>-0.0136092042593523</v>
+      </c>
+      <c r="E238">
+        <v>3.227639303241795</v>
+      </c>
+      <c r="F238">
+        <v>2.621254253488535</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>26</v>
+      </c>
+      <c r="B239" t="s">
+        <v>30</v>
+      </c>
+      <c r="C239">
+        <v>0.0001</v>
+      </c>
+      <c r="D239">
+        <v>-0.05635567742930303</v>
+      </c>
+      <c r="E239">
+        <v>3.294995363894261</v>
+      </c>
+      <c r="F239">
+        <v>2.713399178496899</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>24</v>
+      </c>
+      <c r="B240" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240">
+        <v>0.001</v>
+      </c>
+      <c r="D240">
+        <v>-0.06240664906311277</v>
+      </c>
+      <c r="E240">
+        <v>3.304419014231899</v>
+      </c>
+      <c r="F240">
+        <v>2.621993046458757</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>28</v>
+      </c>
+      <c r="B241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241">
+        <v>0.001</v>
+      </c>
+      <c r="D241">
+        <v>-0.06823535287798443</v>
+      </c>
+      <c r="E241">
+        <v>3.313471167029199</v>
+      </c>
+      <c r="F241">
+        <v>2.649481943791619</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>13</v>
+      </c>
+      <c r="B242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242">
+        <v>0.001</v>
+      </c>
+      <c r="D242">
+        <v>-0.142146953000849</v>
+      </c>
+      <c r="E242">
+        <v>3.426184257115198</v>
+      </c>
+      <c r="F242">
+        <v>2.821172920146463</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>28</v>
+      </c>
+      <c r="B243" t="s">
+        <v>30</v>
+      </c>
+      <c r="C243">
+        <v>0.001</v>
+      </c>
+      <c r="D243">
+        <v>-0.1758733457000263</v>
+      </c>
+      <c r="E243">
+        <v>3.476402035154435</v>
+      </c>
+      <c r="F243">
+        <v>2.79277113482703</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>27</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244">
+        <v>0.0001</v>
+      </c>
+      <c r="D244">
+        <v>-0.1882202744584194</v>
+      </c>
+      <c r="E244">
+        <v>3.494605866876723</v>
+      </c>
+      <c r="F244">
+        <v>2.808718143828123</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>13</v>
+      </c>
+      <c r="B245" t="s">
+        <v>30</v>
+      </c>
+      <c r="C245">
+        <v>0.0001</v>
+      </c>
+      <c r="D245">
+        <v>-0.2121915133973549</v>
+      </c>
+      <c r="E245">
+        <v>3.529680064456845</v>
+      </c>
+      <c r="F245">
+        <v>2.712845861577303</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>26</v>
+      </c>
+      <c r="B246" t="s">
+        <v>30</v>
+      </c>
+      <c r="C246">
+        <v>0.001</v>
+      </c>
+      <c r="D246">
+        <v>-0.2277382428795873</v>
+      </c>
+      <c r="E246">
+        <v>3.552242569105454</v>
+      </c>
+      <c r="F246">
+        <v>3.084917748508046</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>27</v>
+      </c>
+      <c r="B247" t="s">
+        <v>30</v>
+      </c>
+      <c r="C247">
+        <v>0.0001</v>
+      </c>
+      <c r="D247">
+        <v>-0.2372292214720664</v>
+      </c>
+      <c r="E247">
+        <v>3.565946366452743</v>
+      </c>
+      <c r="F247">
+        <v>2.926937508222364</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>24</v>
+      </c>
+      <c r="B248" t="s">
+        <v>14</v>
+      </c>
+      <c r="C248">
+        <v>0.0001</v>
+      </c>
+      <c r="D248">
+        <v>-0.267463547833904</v>
+      </c>
+      <c r="E248">
+        <v>3.609254124417001</v>
+      </c>
+      <c r="F248">
+        <v>2.965938895685844</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>13</v>
+      </c>
+      <c r="B249" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249">
+        <v>0.0001</v>
+      </c>
+      <c r="D249">
+        <v>-0.2966232685503802</v>
+      </c>
+      <c r="E249">
+        <v>3.650535935608096</v>
+      </c>
+      <c r="F249">
+        <v>2.771318377826382</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>29</v>
+      </c>
+      <c r="B250" t="s">
+        <v>30</v>
+      </c>
+      <c r="C250">
+        <v>0.0001</v>
+      </c>
+      <c r="D250">
+        <v>-0.3414553445353081</v>
+      </c>
+      <c r="E250">
+        <v>3.713110147386522</v>
+      </c>
+      <c r="F250">
+        <v>2.294260441489465</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>28</v>
+      </c>
+      <c r="B251" t="s">
+        <v>30</v>
+      </c>
+      <c r="C251">
+        <v>0.0001</v>
+      </c>
+      <c r="D251">
+        <v>-0.3534308157982087</v>
+      </c>
+      <c r="E251">
+        <v>3.729647203405037</v>
+      </c>
+      <c r="F251">
+        <v>2.586859939498824</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>28</v>
+      </c>
+      <c r="B252" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252">
+        <v>0.0001</v>
+      </c>
+      <c r="D252">
+        <v>-0.40416182148501</v>
+      </c>
+      <c r="E252">
+        <v>3.798903859124556</v>
+      </c>
+      <c r="F252">
+        <v>2.895370489082532</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>29</v>
+      </c>
+      <c r="B253" t="s">
+        <v>30</v>
+      </c>
+      <c r="C253">
+        <v>0.001</v>
+      </c>
+      <c r="D253">
+        <v>-0.6204190748666909</v>
+      </c>
+      <c r="E253">
+        <v>4.080969940878073</v>
+      </c>
+      <c r="F253">
+        <v>3.033181607253352</v>
       </c>
     </row>
   </sheetData>
